--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T03:53:40.467Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T04:13:22.232Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3298,7 +3298,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T03:53:41.224Z</t>
+    <t>2026-10-02T04:13:22.981Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -13291,7 +13291,7 @@
         <v>1006</v>
       </c>
       <c r="E2" s="2">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -13409,7 +13409,7 @@
         <v>1006</v>
       </c>
       <c r="E8" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -13427,7 +13427,7 @@
         <v>1006</v>
       </c>
       <c r="E9" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -13445,7 +13445,7 @@
         <v>1006</v>
       </c>
       <c r="E10" s="2">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -13463,7 +13463,7 @@
         <v>1006</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -13481,7 +13481,7 @@
         <v>1006</v>
       </c>
       <c r="E12" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -13499,7 +13499,7 @@
         <v>1006</v>
       </c>
       <c r="E13" s="2">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -13577,7 +13577,7 @@
         <v>1006</v>
       </c>
       <c r="E17" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -13595,7 +13595,7 @@
         <v>1006</v>
       </c>
       <c r="E18" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -13653,7 +13653,7 @@
         <v>1006</v>
       </c>
       <c r="E21" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -13691,7 +13691,7 @@
         <v>1006</v>
       </c>
       <c r="E23" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -13727,7 +13727,7 @@
         <v>1006</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -13745,7 +13745,7 @@
         <v>1006</v>
       </c>
       <c r="E26" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -13763,7 +13763,7 @@
         <v>1006</v>
       </c>
       <c r="E27" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -13781,7 +13781,7 @@
         <v>1006</v>
       </c>
       <c r="E28" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -13799,7 +13799,7 @@
         <v>1006</v>
       </c>
       <c r="E29" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -13817,7 +13817,7 @@
         <v>1006</v>
       </c>
       <c r="E30" s="2">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -13835,7 +13835,7 @@
         <v>1006</v>
       </c>
       <c r="E31" s="2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -13873,7 +13873,7 @@
         <v>1006</v>
       </c>
       <c r="E33" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -13891,7 +13891,7 @@
         <v>1006</v>
       </c>
       <c r="E34" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -13949,7 +13949,7 @@
         <v>1006</v>
       </c>
       <c r="E37" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -14005,7 +14005,7 @@
         <v>1006</v>
       </c>
       <c r="E40" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -14103,7 +14103,7 @@
         <v>1006</v>
       </c>
       <c r="E45" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -14121,7 +14121,7 @@
         <v>1006</v>
       </c>
       <c r="E46" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -14139,7 +14139,7 @@
         <v>1006</v>
       </c>
       <c r="E47" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -14177,7 +14177,7 @@
         <v>1006</v>
       </c>
       <c r="E49" s="2">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -14195,7 +14195,7 @@
         <v>1006</v>
       </c>
       <c r="E50" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -14213,7 +14213,7 @@
         <v>1006</v>
       </c>
       <c r="E51" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -14331,7 +14331,7 @@
         <v>1006</v>
       </c>
       <c r="E57" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -14349,7 +14349,7 @@
         <v>1006</v>
       </c>
       <c r="E58" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -14387,7 +14387,7 @@
         <v>1006</v>
       </c>
       <c r="E60" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -14485,7 +14485,7 @@
         <v>1006</v>
       </c>
       <c r="E65" s="2">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -14521,7 +14521,7 @@
         <v>1006</v>
       </c>
       <c r="E67" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -14579,7 +14579,7 @@
         <v>1006</v>
       </c>
       <c r="E70" s="2">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -14597,7 +14597,7 @@
         <v>1006</v>
       </c>
       <c r="E71" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -14615,7 +14615,7 @@
         <v>1006</v>
       </c>
       <c r="E72" s="2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -14653,7 +14653,7 @@
         <v>1006</v>
       </c>
       <c r="E74" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -14671,7 +14671,7 @@
         <v>1006</v>
       </c>
       <c r="E75" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -14689,7 +14689,7 @@
         <v>1006</v>
       </c>
       <c r="E76" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -14707,7 +14707,7 @@
         <v>1006</v>
       </c>
       <c r="E77" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -14765,7 +14765,7 @@
         <v>1006</v>
       </c>
       <c r="E80" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -14783,7 +14783,7 @@
         <v>1006</v>
       </c>
       <c r="E81" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -14801,7 +14801,7 @@
         <v>1006</v>
       </c>
       <c r="E82" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -14879,7 +14879,7 @@
         <v>1006</v>
       </c>
       <c r="E86" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -14897,7 +14897,7 @@
         <v>1006</v>
       </c>
       <c r="E87" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -14915,7 +14915,7 @@
         <v>1006</v>
       </c>
       <c r="E88" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -14933,7 +14933,7 @@
         <v>1006</v>
       </c>
       <c r="E89" s="2">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -14951,7 +14951,7 @@
         <v>1006</v>
       </c>
       <c r="E90" s="2">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -14989,7 +14989,7 @@
         <v>1006</v>
       </c>
       <c r="E92" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -15027,7 +15027,7 @@
         <v>1006</v>
       </c>
       <c r="E94" s="2">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -15105,7 +15105,7 @@
         <v>1006</v>
       </c>
       <c r="E98" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -15223,7 +15223,7 @@
         <v>1006</v>
       </c>
       <c r="E104" s="2">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -15261,7 +15261,7 @@
         <v>1006</v>
       </c>
       <c r="E106" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -15399,7 +15399,7 @@
         <v>1006</v>
       </c>
       <c r="E113" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -15495,7 +15495,7 @@
         <v>1006</v>
       </c>
       <c r="E118" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -15513,7 +15513,7 @@
         <v>1006</v>
       </c>
       <c r="E119" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -15531,7 +15531,7 @@
         <v>1006</v>
       </c>
       <c r="E120" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -15549,7 +15549,7 @@
         <v>1006</v>
       </c>
       <c r="E121" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -15567,7 +15567,7 @@
         <v>1006</v>
       </c>
       <c r="E122" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -15603,7 +15603,7 @@
         <v>1006</v>
       </c>
       <c r="E124" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -15657,7 +15657,7 @@
         <v>1006</v>
       </c>
       <c r="E127" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -15675,7 +15675,7 @@
         <v>1006</v>
       </c>
       <c r="E128" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -15693,7 +15693,7 @@
         <v>1006</v>
       </c>
       <c r="E129" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -15711,7 +15711,7 @@
         <v>1006</v>
       </c>
       <c r="E130" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -15729,7 +15729,7 @@
         <v>1006</v>
       </c>
       <c r="E131" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -15747,7 +15747,7 @@
         <v>1006</v>
       </c>
       <c r="E132" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -15765,7 +15765,7 @@
         <v>1006</v>
       </c>
       <c r="E133" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F133" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T04:13:22.232Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:07:58.380Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3298,7 +3298,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T04:13:22.981Z</t>
+    <t>2026-10-02T15:08:02.074Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -13291,7 +13291,7 @@
         <v>1006</v>
       </c>
       <c r="E2" s="2">
-        <v>499</v>
+        <v>529</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -13409,7 +13409,7 @@
         <v>1006</v>
       </c>
       <c r="E8" s="2">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -13427,7 +13427,7 @@
         <v>1006</v>
       </c>
       <c r="E9" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -13445,7 +13445,7 @@
         <v>1006</v>
       </c>
       <c r="E10" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -13463,7 +13463,7 @@
         <v>1006</v>
       </c>
       <c r="E11" s="2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -13481,7 +13481,7 @@
         <v>1006</v>
       </c>
       <c r="E12" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -13499,7 +13499,7 @@
         <v>1006</v>
       </c>
       <c r="E13" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -13577,7 +13577,7 @@
         <v>1006</v>
       </c>
       <c r="E17" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -13595,7 +13595,7 @@
         <v>1006</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -13727,7 +13727,7 @@
         <v>1006</v>
       </c>
       <c r="E25" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -13745,7 +13745,7 @@
         <v>1006</v>
       </c>
       <c r="E26" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -13763,7 +13763,7 @@
         <v>1006</v>
       </c>
       <c r="E27" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -13781,7 +13781,7 @@
         <v>1006</v>
       </c>
       <c r="E28" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -13799,7 +13799,7 @@
         <v>1006</v>
       </c>
       <c r="E29" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -13817,7 +13817,7 @@
         <v>1006</v>
       </c>
       <c r="E30" s="2">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -13835,7 +13835,7 @@
         <v>1006</v>
       </c>
       <c r="E31" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -13873,7 +13873,7 @@
         <v>1006</v>
       </c>
       <c r="E33" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -13891,7 +13891,7 @@
         <v>1006</v>
       </c>
       <c r="E34" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -13949,7 +13949,7 @@
         <v>1006</v>
       </c>
       <c r="E37" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -13987,7 +13987,7 @@
         <v>1006</v>
       </c>
       <c r="E39" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -14005,7 +14005,7 @@
         <v>1006</v>
       </c>
       <c r="E40" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -14139,7 +14139,7 @@
         <v>1006</v>
       </c>
       <c r="E47" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -14177,7 +14177,7 @@
         <v>1006</v>
       </c>
       <c r="E49" s="2">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -14195,7 +14195,7 @@
         <v>1006</v>
       </c>
       <c r="E50" s="2">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -14213,7 +14213,7 @@
         <v>1006</v>
       </c>
       <c r="E51" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -14331,7 +14331,7 @@
         <v>1006</v>
       </c>
       <c r="E57" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -14349,7 +14349,7 @@
         <v>1006</v>
       </c>
       <c r="E58" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -14387,7 +14387,7 @@
         <v>1006</v>
       </c>
       <c r="E60" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -14485,7 +14485,7 @@
         <v>1006</v>
       </c>
       <c r="E65" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -14503,7 +14503,7 @@
         <v>1006</v>
       </c>
       <c r="E66" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -14521,7 +14521,7 @@
         <v>1006</v>
       </c>
       <c r="E67" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -14579,7 +14579,7 @@
         <v>1006</v>
       </c>
       <c r="E70" s="2">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -14597,7 +14597,7 @@
         <v>1006</v>
       </c>
       <c r="E71" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -14615,7 +14615,7 @@
         <v>1006</v>
       </c>
       <c r="E72" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -14653,7 +14653,7 @@
         <v>1006</v>
       </c>
       <c r="E74" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -14671,7 +14671,7 @@
         <v>1006</v>
       </c>
       <c r="E75" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -14689,7 +14689,7 @@
         <v>1006</v>
       </c>
       <c r="E76" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -14707,7 +14707,7 @@
         <v>1006</v>
       </c>
       <c r="E77" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -14765,7 +14765,7 @@
         <v>1006</v>
       </c>
       <c r="E80" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -14783,7 +14783,7 @@
         <v>1006</v>
       </c>
       <c r="E81" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -14801,7 +14801,7 @@
         <v>1006</v>
       </c>
       <c r="E82" s="2">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -14879,7 +14879,7 @@
         <v>1006</v>
       </c>
       <c r="E86" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -14897,7 +14897,7 @@
         <v>1006</v>
       </c>
       <c r="E87" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -14915,7 +14915,7 @@
         <v>1006</v>
       </c>
       <c r="E88" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -14933,7 +14933,7 @@
         <v>1006</v>
       </c>
       <c r="E89" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -14951,7 +14951,7 @@
         <v>1006</v>
       </c>
       <c r="E90" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -14989,7 +14989,7 @@
         <v>1006</v>
       </c>
       <c r="E92" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -15027,7 +15027,7 @@
         <v>1006</v>
       </c>
       <c r="E94" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -15105,7 +15105,7 @@
         <v>1006</v>
       </c>
       <c r="E98" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -15223,7 +15223,7 @@
         <v>1006</v>
       </c>
       <c r="E104" s="2">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -15261,7 +15261,7 @@
         <v>1006</v>
       </c>
       <c r="E106" s="2">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -15399,7 +15399,7 @@
         <v>1006</v>
       </c>
       <c r="E113" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -15477,7 +15477,7 @@
         <v>1006</v>
       </c>
       <c r="E117" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -15495,7 +15495,7 @@
         <v>1006</v>
       </c>
       <c r="E118" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -15513,7 +15513,7 @@
         <v>1006</v>
       </c>
       <c r="E119" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -15531,7 +15531,7 @@
         <v>1006</v>
       </c>
       <c r="E120" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -15549,7 +15549,7 @@
         <v>1006</v>
       </c>
       <c r="E121" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -15567,7 +15567,7 @@
         <v>1006</v>
       </c>
       <c r="E122" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -15585,7 +15585,7 @@
         <v>1006</v>
       </c>
       <c r="E123" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -15603,7 +15603,7 @@
         <v>1006</v>
       </c>
       <c r="E124" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -15621,7 +15621,7 @@
         <v>1006</v>
       </c>
       <c r="E125" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -15639,7 +15639,7 @@
         <v>1006</v>
       </c>
       <c r="E126" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -15711,7 +15711,7 @@
         <v>1006</v>
       </c>
       <c r="E130" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -15729,7 +15729,7 @@
         <v>1006</v>
       </c>
       <c r="E131" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -15747,7 +15747,7 @@
         <v>1006</v>
       </c>
       <c r="E132" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F132" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:07:58.380Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:29:14.556Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3298,7 +3298,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:02.074Z</t>
+    <t>2026-10-02T15:29:15.369Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -13291,7 +13291,7 @@
         <v>1006</v>
       </c>
       <c r="E2" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -13427,7 +13427,7 @@
         <v>1006</v>
       </c>
       <c r="E9" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -13445,7 +13445,7 @@
         <v>1006</v>
       </c>
       <c r="E10" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -13463,7 +13463,7 @@
         <v>1006</v>
       </c>
       <c r="E11" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -13481,7 +13481,7 @@
         <v>1006</v>
       </c>
       <c r="E12" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -13499,7 +13499,7 @@
         <v>1006</v>
       </c>
       <c r="E13" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -13577,7 +13577,7 @@
         <v>1006</v>
       </c>
       <c r="E17" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -13595,7 +13595,7 @@
         <v>1006</v>
       </c>
       <c r="E18" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -13653,7 +13653,7 @@
         <v>1006</v>
       </c>
       <c r="E21" s="2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -13691,7 +13691,7 @@
         <v>1006</v>
       </c>
       <c r="E23" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -13727,7 +13727,7 @@
         <v>1006</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -13763,7 +13763,7 @@
         <v>1006</v>
       </c>
       <c r="E27" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -13781,7 +13781,7 @@
         <v>1006</v>
       </c>
       <c r="E28" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -13799,7 +13799,7 @@
         <v>1006</v>
       </c>
       <c r="E29" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -13817,7 +13817,7 @@
         <v>1006</v>
       </c>
       <c r="E30" s="2">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -13835,7 +13835,7 @@
         <v>1006</v>
       </c>
       <c r="E31" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -13873,7 +13873,7 @@
         <v>1006</v>
       </c>
       <c r="E33" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -13891,7 +13891,7 @@
         <v>1006</v>
       </c>
       <c r="E34" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -13949,7 +13949,7 @@
         <v>1006</v>
       </c>
       <c r="E37" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -13987,7 +13987,7 @@
         <v>1006</v>
       </c>
       <c r="E39" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -14005,7 +14005,7 @@
         <v>1006</v>
       </c>
       <c r="E40" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -14103,7 +14103,7 @@
         <v>1006</v>
       </c>
       <c r="E45" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -14139,7 +14139,7 @@
         <v>1006</v>
       </c>
       <c r="E47" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -14177,7 +14177,7 @@
         <v>1006</v>
       </c>
       <c r="E49" s="2">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -14195,7 +14195,7 @@
         <v>1006</v>
       </c>
       <c r="E50" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -14213,7 +14213,7 @@
         <v>1006</v>
       </c>
       <c r="E51" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -14331,7 +14331,7 @@
         <v>1006</v>
       </c>
       <c r="E57" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -14349,7 +14349,7 @@
         <v>1006</v>
       </c>
       <c r="E58" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -14387,7 +14387,7 @@
         <v>1006</v>
       </c>
       <c r="E60" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -14485,7 +14485,7 @@
         <v>1006</v>
       </c>
       <c r="E65" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -14503,7 +14503,7 @@
         <v>1006</v>
       </c>
       <c r="E66" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -14521,7 +14521,7 @@
         <v>1006</v>
       </c>
       <c r="E67" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -14579,7 +14579,7 @@
         <v>1006</v>
       </c>
       <c r="E70" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -14597,7 +14597,7 @@
         <v>1006</v>
       </c>
       <c r="E71" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -14615,7 +14615,7 @@
         <v>1006</v>
       </c>
       <c r="E72" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -14653,7 +14653,7 @@
         <v>1006</v>
       </c>
       <c r="E74" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -14671,7 +14671,7 @@
         <v>1006</v>
       </c>
       <c r="E75" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -14689,7 +14689,7 @@
         <v>1006</v>
       </c>
       <c r="E76" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -14707,7 +14707,7 @@
         <v>1006</v>
       </c>
       <c r="E77" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -14765,7 +14765,7 @@
         <v>1006</v>
       </c>
       <c r="E80" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -14801,7 +14801,7 @@
         <v>1006</v>
       </c>
       <c r="E82" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -14879,7 +14879,7 @@
         <v>1006</v>
       </c>
       <c r="E86" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -14897,7 +14897,7 @@
         <v>1006</v>
       </c>
       <c r="E87" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -14915,7 +14915,7 @@
         <v>1006</v>
       </c>
       <c r="E88" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -14933,7 +14933,7 @@
         <v>1006</v>
       </c>
       <c r="E89" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -14951,7 +14951,7 @@
         <v>1006</v>
       </c>
       <c r="E90" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -14989,7 +14989,7 @@
         <v>1006</v>
       </c>
       <c r="E92" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -15027,7 +15027,7 @@
         <v>1006</v>
       </c>
       <c r="E94" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -15105,7 +15105,7 @@
         <v>1006</v>
       </c>
       <c r="E98" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -15223,7 +15223,7 @@
         <v>1006</v>
       </c>
       <c r="E104" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -15261,7 +15261,7 @@
         <v>1006</v>
       </c>
       <c r="E106" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -15399,7 +15399,7 @@
         <v>1006</v>
       </c>
       <c r="E113" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -15477,7 +15477,7 @@
         <v>1006</v>
       </c>
       <c r="E117" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -15495,7 +15495,7 @@
         <v>1006</v>
       </c>
       <c r="E118" s="2">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -15531,7 +15531,7 @@
         <v>1006</v>
       </c>
       <c r="E120" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -15549,7 +15549,7 @@
         <v>1006</v>
       </c>
       <c r="E121" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -15567,7 +15567,7 @@
         <v>1006</v>
       </c>
       <c r="E122" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -15585,7 +15585,7 @@
         <v>1006</v>
       </c>
       <c r="E123" s="2">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -15603,7 +15603,7 @@
         <v>1006</v>
       </c>
       <c r="E124" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -15657,7 +15657,7 @@
         <v>1006</v>
       </c>
       <c r="E127" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -15675,7 +15675,7 @@
         <v>1006</v>
       </c>
       <c r="E128" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -15693,7 +15693,7 @@
         <v>1006</v>
       </c>
       <c r="E129" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -15711,7 +15711,7 @@
         <v>1006</v>
       </c>
       <c r="E130" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -15729,7 +15729,7 @@
         <v>1006</v>
       </c>
       <c r="E131" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -15747,7 +15747,7 @@
         <v>1006</v>
       </c>
       <c r="E132" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -15765,7 +15765,7 @@
         <v>1006</v>
       </c>
       <c r="E133" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F133" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
@@ -169,7 +169,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:27:08.844Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:43:34.707Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4476,7 +4476,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T19:27:22.211Z</t>
+    <t>2026-10-02T19:43:35.538Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -19882,7 +19882,7 @@
         <v>1008</v>
       </c>
       <c r="E2" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -20000,7 +20000,7 @@
         <v>1008</v>
       </c>
       <c r="E8" s="2">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -20018,7 +20018,7 @@
         <v>1008</v>
       </c>
       <c r="E9" s="2">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -20036,7 +20036,7 @@
         <v>1008</v>
       </c>
       <c r="E10" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -20072,7 +20072,7 @@
         <v>1008</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -20090,7 +20090,7 @@
         <v>1008</v>
       </c>
       <c r="E13" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -20168,7 +20168,7 @@
         <v>1008</v>
       </c>
       <c r="E17" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -20186,7 +20186,7 @@
         <v>1008</v>
       </c>
       <c r="E18" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -20244,7 +20244,7 @@
         <v>1008</v>
       </c>
       <c r="E21" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -20282,7 +20282,7 @@
         <v>1008</v>
       </c>
       <c r="E23" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -20300,7 +20300,7 @@
         <v>1008</v>
       </c>
       <c r="E24" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -20318,7 +20318,7 @@
         <v>1008</v>
       </c>
       <c r="E25" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -20354,7 +20354,7 @@
         <v>1008</v>
       </c>
       <c r="E27" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -20372,7 +20372,7 @@
         <v>1008</v>
       </c>
       <c r="E28" s="2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -20390,7 +20390,7 @@
         <v>1008</v>
       </c>
       <c r="E29" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -20408,7 +20408,7 @@
         <v>1008</v>
       </c>
       <c r="E30" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -20426,7 +20426,7 @@
         <v>1008</v>
       </c>
       <c r="E31" s="2">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -20464,7 +20464,7 @@
         <v>1008</v>
       </c>
       <c r="E33" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -20482,7 +20482,7 @@
         <v>1008</v>
       </c>
       <c r="E34" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -20540,7 +20540,7 @@
         <v>1008</v>
       </c>
       <c r="E37" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -20578,7 +20578,7 @@
         <v>1008</v>
       </c>
       <c r="E39" s="2">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -20596,7 +20596,7 @@
         <v>1008</v>
       </c>
       <c r="E40" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -20694,7 +20694,7 @@
         <v>1008</v>
       </c>
       <c r="E45" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -20712,7 +20712,7 @@
         <v>1008</v>
       </c>
       <c r="E46" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -20768,7 +20768,7 @@
         <v>1008</v>
       </c>
       <c r="E49" s="2">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -20786,7 +20786,7 @@
         <v>1008</v>
       </c>
       <c r="E50" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -20804,7 +20804,7 @@
         <v>1008</v>
       </c>
       <c r="E51" s="2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -20922,7 +20922,7 @@
         <v>1008</v>
       </c>
       <c r="E57" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -20978,7 +20978,7 @@
         <v>1008</v>
       </c>
       <c r="E60" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -21076,7 +21076,7 @@
         <v>1008</v>
       </c>
       <c r="E65" s="2">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -21094,7 +21094,7 @@
         <v>1008</v>
       </c>
       <c r="E66" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -21112,7 +21112,7 @@
         <v>1008</v>
       </c>
       <c r="E67" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -21170,7 +21170,7 @@
         <v>1008</v>
       </c>
       <c r="E70" s="2">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -21206,7 +21206,7 @@
         <v>1008</v>
       </c>
       <c r="E72" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -21244,7 +21244,7 @@
         <v>1008</v>
       </c>
       <c r="E74" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -21262,7 +21262,7 @@
         <v>1008</v>
       </c>
       <c r="E75" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -21280,7 +21280,7 @@
         <v>1008</v>
       </c>
       <c r="E76" s="2">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -21298,7 +21298,7 @@
         <v>1008</v>
       </c>
       <c r="E77" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -21356,7 +21356,7 @@
         <v>1008</v>
       </c>
       <c r="E80" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -21374,7 +21374,7 @@
         <v>1008</v>
       </c>
       <c r="E81" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -21392,7 +21392,7 @@
         <v>1008</v>
       </c>
       <c r="E82" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -21470,7 +21470,7 @@
         <v>1008</v>
       </c>
       <c r="E86" s="2">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -21488,7 +21488,7 @@
         <v>1008</v>
       </c>
       <c r="E87" s="2">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -21506,7 +21506,7 @@
         <v>1008</v>
       </c>
       <c r="E88" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -21524,7 +21524,7 @@
         <v>1008</v>
       </c>
       <c r="E89" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -21542,7 +21542,7 @@
         <v>1008</v>
       </c>
       <c r="E90" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -21580,7 +21580,7 @@
         <v>1008</v>
       </c>
       <c r="E92" s="2">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -21618,7 +21618,7 @@
         <v>1008</v>
       </c>
       <c r="E94" s="2">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -21696,7 +21696,7 @@
         <v>1008</v>
       </c>
       <c r="E98" s="2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -21814,7 +21814,7 @@
         <v>1008</v>
       </c>
       <c r="E104" s="2">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -21852,7 +21852,7 @@
         <v>1008</v>
       </c>
       <c r="E106" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -21990,7 +21990,7 @@
         <v>1008</v>
       </c>
       <c r="E113" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -22068,7 +22068,7 @@
         <v>1008</v>
       </c>
       <c r="E117" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -22086,7 +22086,7 @@
         <v>1008</v>
       </c>
       <c r="E118" s="2">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -22104,7 +22104,7 @@
         <v>1008</v>
       </c>
       <c r="E119" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -22122,7 +22122,7 @@
         <v>1008</v>
       </c>
       <c r="E120" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -22140,7 +22140,7 @@
         <v>1008</v>
       </c>
       <c r="E121" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -22158,7 +22158,7 @@
         <v>1008</v>
       </c>
       <c r="E122" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -22176,7 +22176,7 @@
         <v>1008</v>
       </c>
       <c r="E123" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -22212,7 +22212,7 @@
         <v>1008</v>
       </c>
       <c r="E125" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -22230,7 +22230,7 @@
         <v>1008</v>
       </c>
       <c r="E126" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -22248,7 +22248,7 @@
         <v>1008</v>
       </c>
       <c r="E127" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -22266,7 +22266,7 @@
         <v>1008</v>
       </c>
       <c r="E128" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -22284,7 +22284,7 @@
         <v>1008</v>
       </c>
       <c r="E129" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -22320,7 +22320,7 @@
         <v>1008</v>
       </c>
       <c r="E131" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -22338,7 +22338,7 @@
         <v>1008</v>
       </c>
       <c r="E132" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F132" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
@@ -10,20 +10,21 @@
     <sheet sheetId="4" name="Test Cases" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Execution" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Defects" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Coverage" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Attribute coverage" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Traceability by story" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Traceability matrix" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Approvals" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Skills" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Hand-overs" state="visible" r:id="rId16"/>
+    <sheet sheetId="7" name="Fixed and certified" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Coverage" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Attribute coverage" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Traceability by story" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Traceability matrix" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Approvals" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Skills" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Hand-overs" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5608" uniqueCount="1554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5650" uniqueCount="1574">
   <si>
     <t>Metric</t>
   </si>
@@ -115,7 +116,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Functional (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 132 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 74 passed and 0 failed (pass rate 100%). No defects were raised.</t>
+    <t>Hotel booking baseline · Functional (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 132 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 71 passed and 3 failed (pass rate 95.9%). 3 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-003 9 rooms in one search are rejected: returns 200 instead of 400.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -163,13 +164,13 @@
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
+    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:43:34.707Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:04:42.395Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2797,7 +2798,7 @@
     <t>expiresAt - createdAt = 30 min; timeout behaviour shown; no reservation exists</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-122, BR-122</t>
+    <t>AQPI-15, REQ-122, BR-122</t>
   </si>
   <si>
     <t>TC-F-113</t>
@@ -2823,7 +2824,7 @@
     <t>Revalidation requires acknowledgement; first submit HTTP 409 PRICE_CHANGE_REQUIRES_ACKNOWLEDGEMENT; after acknowledging HTTP 201</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-123, BR-123</t>
+    <t>AQPI-17, REQ-123, BR-123</t>
   </si>
   <si>
     <t>TC-F-114</t>
@@ -2862,7 +2863,7 @@
     <t>First 3 resends HTTP 202, the next HTTP 429; still one reservation</t>
   </si>
   <si>
-    <t>notification-service/src/main/resources/notification-service.yml, REQ-124, BR-124</t>
+    <t>AQPI-26, REQ-124, BR-124</t>
   </si>
   <si>
     <t>TC-F-116</t>
@@ -2881,7 +2882,7 @@
     <t>HTTP 400 IDEMPOTENCY_KEY_REQUIRED</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml, REQ-125, BR-125</t>
+    <t>AQPI-21, REQ-125, BR-125</t>
   </si>
   <si>
     <t>TC-F-117</t>
@@ -2931,7 +2932,7 @@
     <t>HTTP 200 with a searchId</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-126, BR-126</t>
+    <t>AQPI-4, REQ-126, BR-126</t>
   </si>
   <si>
     <t>TC-F-120</t>
@@ -2997,7 +2998,7 @@
     <t>occupancy.adults=4; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-127, BR-127</t>
+    <t>AQPI-4, REQ-127, BR-127</t>
   </si>
   <si>
     <t>TC-F-124</t>
@@ -3069,7 +3070,7 @@
     <t>stay.checkInOffsetDays=500; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-128, BR-128</t>
+    <t>AQPI-4, REQ-128, BR-128</t>
   </si>
   <si>
     <t>TC-F-128</t>
@@ -3111,6 +3112,9 @@
     <t>Manual test case - not automated, not executed</t>
   </si>
   <si>
+    <t>failed</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -3135,6 +3139,75 @@
     <t>Movement</t>
   </si>
   <si>
+    <t>DEF-001</t>
+  </si>
+  <si>
+    <t>A price change within 1% does not need acknowledgement: returns true instead of false</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>AQPI-17</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-17 in the platform</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>expect(rv.body.requiresAcknowledgement).toBe(false);</t>
+  </si>
+  <si>
+    <t>DEF-002</t>
+  </si>
+  <si>
+    <t>A key shorter than 8 characters is refused: returns 201 instead of 400</t>
+  </si>
+  <si>
+    <t>AQPI-21</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-21 in the platform</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>expect(r.status).toBe(400);</t>
+  </si>
+  <si>
+    <t>DEF-003</t>
+  </si>
+  <si>
+    <t>9 rooms in one search are rejected: returns 200 instead of 400</t>
+  </si>
+  <si>
+    <t>AQPI-4</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-4 in the platform</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>First seen</t>
+  </si>
+  <si>
+    <t>Retested in</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
     <t>Text</t>
   </si>
   <si>
@@ -3153,6 +3226,9 @@
     <t>designed only (manual)</t>
   </si>
   <si>
+    <t>executed - failing</t>
+  </si>
+  <si>
     <t>Attribute</t>
   </si>
   <si>
@@ -3201,6 +3277,9 @@
     <t>TC-F-016, TC-F-126</t>
   </si>
   <si>
+    <t>exercised - failing</t>
+  </si>
+  <si>
     <t>occupancy.adults</t>
   </si>
   <si>
@@ -3330,12 +3409,12 @@
     <t>3.1 Search hotels by destination and date range</t>
   </si>
   <si>
-    <t>AQPI-4</t>
-  </si>
-  <si>
     <t>3.2 Validate occupancy and stay criteria</t>
   </si>
   <si>
+    <t>failing</t>
+  </si>
+  <si>
     <t>AQPI-5</t>
   </si>
   <si>
@@ -3408,9 +3487,6 @@
     <t>6.2 Add, update, and remove ancillaries</t>
   </si>
   <si>
-    <t>AQPI-17</t>
-  </si>
-  <si>
     <t>6.3 Review cart and total price</t>
   </si>
   <si>
@@ -3432,9 +3508,6 @@
     <t>7.2 Capture and authorize payment</t>
   </si>
   <si>
-    <t>AQPI-21</t>
-  </si>
-  <si>
     <t>7.3 Create reservation idempotently</t>
   </si>
   <si>
@@ -4347,9 +4420,6 @@
     <t>TD-F-111</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml</t>
-  </si>
-  <si>
     <t>BR-122</t>
   </si>
   <si>
@@ -4371,9 +4441,6 @@
     <t>TD-F-114</t>
   </si>
   <si>
-    <t>notification-service/src/main/resources/notification-service.yml</t>
-  </si>
-  <si>
     <t>BR-124</t>
   </si>
   <si>
@@ -4383,9 +4450,6 @@
     <t>br-124-resend-limit.spec.js</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml</t>
-  </si>
-  <si>
     <t>BR-125</t>
   </si>
   <si>
@@ -4401,9 +4465,6 @@
     <t>TD-F-118</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml</t>
-  </si>
-  <si>
     <t>BR-126</t>
   </si>
   <si>
@@ -4476,7 +4537,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T19:43:35.538Z</t>
+    <t>2026-10-02T20:04:43.242Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5243,7 +5304,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5251,7 +5312,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5259,7 +5320,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="2">
-        <v>100</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5275,7 +5336,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5283,7 +5344,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>45.3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5309,6 +5370,1146 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2">
+        <v>7</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2</v>
+      </c>
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2">
+        <v>2</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2">
+        <v>7</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3</v>
+      </c>
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E20" s="2">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2">
+        <v>4</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E21" s="2">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2">
+        <v>6</v>
+      </c>
+      <c r="H21" s="2">
+        <v>6</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E22" s="2">
+        <v>7</v>
+      </c>
+      <c r="F22" s="2">
+        <v>9</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6</v>
+      </c>
+      <c r="H22" s="2">
+        <v>5</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2">
+        <v>3</v>
+      </c>
+      <c r="H23" s="2">
+        <v>3</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2">
+        <v>3</v>
+      </c>
+      <c r="H25" s="2">
+        <v>3</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
+      </c>
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2">
+        <v>2</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2">
+        <v>4</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E29" s="2">
+        <v>5</v>
+      </c>
+      <c r="F29" s="2">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E30" s="2">
+        <v>5</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E31" s="2">
+        <v>3</v>
+      </c>
+      <c r="F31" s="2">
+        <v>3</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M133"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -5328,19 +6529,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1140</v>
+        <v>1164</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1141</v>
+        <v>1165</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1142</v>
+        <v>1166</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1143</v>
+        <v>1167</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>314</v>
@@ -5349,22 +6550,22 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1145</v>
+        <v>1169</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1005</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1147</v>
+        <v>1171</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5378,7 +6579,7 @@
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1148</v>
+        <v>1172</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>326</v>
@@ -5393,10 +6594,10 @@
         <v>337</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1149</v>
+        <v>1173</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1150</v>
+        <v>1174</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1008</v>
@@ -5419,7 +6620,7 @@
         <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1151</v>
+        <v>1175</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>340</v>
@@ -5434,7 +6635,7 @@
         <v>348</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1152</v>
+        <v>1176</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -5458,7 +6659,7 @@
         <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1153</v>
+        <v>1177</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>349</v>
@@ -5473,7 +6674,7 @@
         <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -5497,7 +6698,7 @@
         <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1155</v>
+        <v>1179</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>353</v>
@@ -5512,7 +6713,7 @@
         <v>348</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1156</v>
+        <v>1180</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -5536,7 +6737,7 @@
         <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1157</v>
+        <v>1181</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>357</v>
@@ -5551,7 +6752,7 @@
         <v>348</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1158</v>
+        <v>1182</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -5575,7 +6776,7 @@
         <v>79</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1159</v>
+        <v>1183</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>361</v>
@@ -5590,7 +6791,7 @@
         <v>348</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1160</v>
+        <v>1184</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -5605,7 +6806,7 @@
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>80</v>
@@ -5614,7 +6815,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1161</v>
+        <v>1185</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>365</v>
@@ -5629,10 +6830,10 @@
         <v>337</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1162</v>
+        <v>1186</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1163</v>
+        <v>1187</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1008</v>
@@ -5646,7 +6847,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>82</v>
@@ -5655,7 +6856,7 @@
         <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1164</v>
+        <v>1188</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>373</v>
@@ -5670,10 +6871,10 @@
         <v>337</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1165</v>
+        <v>1189</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1166</v>
+        <v>1190</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1008</v>
@@ -5687,7 +6888,7 @@
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>84</v>
@@ -5696,7 +6897,7 @@
         <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1167</v>
+        <v>1191</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>379</v>
@@ -5711,10 +6912,10 @@
         <v>337</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1168</v>
+        <v>1192</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1169</v>
+        <v>1193</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1008</v>
@@ -5728,7 +6929,7 @@
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>84</v>
@@ -5737,7 +6938,7 @@
         <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1167</v>
+        <v>1191</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>386</v>
@@ -5752,10 +6953,10 @@
         <v>337</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1170</v>
+        <v>1194</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1169</v>
+        <v>1193</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1008</v>
@@ -5769,7 +6970,7 @@
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>84</v>
@@ -5778,7 +6979,7 @@
         <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1167</v>
+        <v>1191</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>392</v>
@@ -5793,10 +6994,10 @@
         <v>337</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1171</v>
+        <v>1195</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1169</v>
+        <v>1193</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1008</v>
@@ -5810,7 +7011,7 @@
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>86</v>
@@ -5819,7 +7020,7 @@
         <v>87</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1172</v>
+        <v>1196</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>398</v>
@@ -5834,10 +7035,10 @@
         <v>337</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1173</v>
+        <v>1197</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1008</v>
@@ -5851,7 +7052,7 @@
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>89</v>
@@ -5860,7 +7061,7 @@
         <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1175</v>
+        <v>1199</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>407</v>
@@ -5875,7 +7076,7 @@
         <v>348</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1176</v>
+        <v>1200</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -5890,7 +7091,7 @@
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -5899,7 +7100,7 @@
         <v>92</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1177</v>
+        <v>1201</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>411</v>
@@ -5914,7 +7115,7 @@
         <v>348</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -5929,7 +7130,7 @@
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>93</v>
@@ -5938,7 +7139,7 @@
         <v>94</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>415</v>
@@ -5953,7 +7154,7 @@
         <v>348</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1180</v>
+        <v>1204</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -5968,7 +7169,7 @@
     </row>
     <row r="17" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1084</v>
+        <v>1037</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>95</v>
@@ -5977,7 +7178,7 @@
         <v>96</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1181</v>
+        <v>1205</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>419</v>
@@ -5992,10 +7193,10 @@
         <v>337</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1182</v>
+        <v>1206</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1183</v>
+        <v>1207</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1008</v>
@@ -6009,7 +7210,7 @@
     </row>
     <row r="18" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1084</v>
+        <v>1037</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>97</v>
@@ -6018,7 +7219,7 @@
         <v>98</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1184</v>
+        <v>1208</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>425</v>
@@ -6033,10 +7234,10 @@
         <v>337</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1185</v>
+        <v>1209</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1186</v>
+        <v>1210</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1008</v>
@@ -6050,7 +7251,7 @@
     </row>
     <row r="19" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1084</v>
+        <v>1037</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>99</v>
@@ -6059,7 +7260,7 @@
         <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1187</v>
+        <v>1211</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>432</v>
@@ -6074,7 +7275,7 @@
         <v>348</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1188</v>
+        <v>1212</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -6089,7 +7290,7 @@
     </row>
     <row r="20" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>1084</v>
+        <v>1037</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>103</v>
@@ -6098,7 +7299,7 @@
         <v>104</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1189</v>
+        <v>1213</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>436</v>
@@ -6113,7 +7314,7 @@
         <v>348</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1190</v>
+        <v>1214</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -6128,7 +7329,7 @@
     </row>
     <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1086</v>
+        <v>1112</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>105</v>
@@ -6137,7 +7338,7 @@
         <v>106</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1191</v>
+        <v>1215</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>440</v>
@@ -6152,10 +7353,10 @@
         <v>337</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1192</v>
+        <v>1216</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1193</v>
+        <v>1217</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>1008</v>
@@ -6169,7 +7370,7 @@
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1086</v>
+        <v>1112</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>107</v>
@@ -6178,7 +7379,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1194</v>
+        <v>1218</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>442</v>
@@ -6193,7 +7394,7 @@
         <v>348</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1195</v>
+        <v>1219</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
@@ -6208,7 +7409,7 @@
     </row>
     <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1086</v>
+        <v>1112</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>109</v>
@@ -6217,7 +7418,7 @@
         <v>110</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>446</v>
@@ -6232,10 +7433,10 @@
         <v>337</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1197</v>
+        <v>1221</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1198</v>
+        <v>1222</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>1008</v>
@@ -6249,7 +7450,7 @@
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1090</v>
+        <v>1116</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>111</v>
@@ -6258,7 +7459,7 @@
         <v>112</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1199</v>
+        <v>1223</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>452</v>
@@ -6273,10 +7474,10 @@
         <v>337</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1200</v>
+        <v>1224</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1201</v>
+        <v>1225</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1008</v>
@@ -6290,7 +7491,7 @@
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1090</v>
+        <v>1116</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>113</v>
@@ -6299,7 +7500,7 @@
         <v>114</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1202</v>
+        <v>1226</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>458</v>
@@ -6314,10 +7515,10 @@
         <v>337</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1203</v>
+        <v>1227</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1204</v>
+        <v>1228</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1008</v>
@@ -6331,7 +7532,7 @@
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>1090</v>
+        <v>1116</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>115</v>
@@ -6340,7 +7541,7 @@
         <v>116</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1205</v>
+        <v>1229</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>463</v>
@@ -6355,10 +7556,10 @@
         <v>337</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1206</v>
+        <v>1230</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1207</v>
+        <v>1231</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1008</v>
@@ -6372,7 +7573,7 @@
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>1090</v>
+        <v>1116</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>117</v>
@@ -6381,7 +7582,7 @@
         <v>118</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1208</v>
+        <v>1232</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>471</v>
@@ -6396,10 +7597,10 @@
         <v>337</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1209</v>
+        <v>1233</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1210</v>
+        <v>1234</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1008</v>
@@ -6413,7 +7614,7 @@
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>1090</v>
+        <v>1116</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>119</v>
@@ -6422,7 +7623,7 @@
         <v>120</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1211</v>
+        <v>1235</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>477</v>
@@ -6437,10 +7638,10 @@
         <v>337</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1212</v>
+        <v>1236</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1213</v>
+        <v>1237</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1008</v>
@@ -6454,7 +7655,7 @@
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1092</v>
+        <v>1118</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>121</v>
@@ -6463,7 +7664,7 @@
         <v>122</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1214</v>
+        <v>1238</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>484</v>
@@ -6478,10 +7679,10 @@
         <v>337</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1215</v>
+        <v>1239</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1216</v>
+        <v>1240</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1008</v>
@@ -6495,7 +7696,7 @@
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1092</v>
+        <v>1118</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>123</v>
@@ -6504,7 +7705,7 @@
         <v>124</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1217</v>
+        <v>1241</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>490</v>
@@ -6519,10 +7720,10 @@
         <v>337</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1218</v>
+        <v>1242</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>1219</v>
+        <v>1243</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>1008</v>
@@ -6536,7 +7737,7 @@
     </row>
     <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1092</v>
+        <v>1118</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>123</v>
@@ -6545,7 +7746,7 @@
         <v>124</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1217</v>
+        <v>1241</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>496</v>
@@ -6560,10 +7761,10 @@
         <v>337</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1220</v>
+        <v>1244</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1219</v>
+        <v>1243</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>1008</v>
@@ -6577,7 +7778,7 @@
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>1092</v>
+        <v>1118</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>125</v>
@@ -6586,7 +7787,7 @@
         <v>126</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1221</v>
+        <v>1245</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>501</v>
@@ -6601,7 +7802,7 @@
         <v>348</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1222</v>
+        <v>1246</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
@@ -6616,7 +7817,7 @@
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1092</v>
+        <v>1118</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>127</v>
@@ -6625,7 +7826,7 @@
         <v>128</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1223</v>
+        <v>1247</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>505</v>
@@ -6640,10 +7841,10 @@
         <v>337</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1224</v>
+        <v>1248</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>1008</v>
@@ -6657,7 +7858,7 @@
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1094</v>
+        <v>1120</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>129</v>
@@ -6666,7 +7867,7 @@
         <v>130</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1226</v>
+        <v>1250</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>511</v>
@@ -6681,10 +7882,10 @@
         <v>337</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1227</v>
+        <v>1251</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1228</v>
+        <v>1252</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1008</v>
@@ -6698,7 +7899,7 @@
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1094</v>
+        <v>1120</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>131</v>
@@ -6707,7 +7908,7 @@
         <v>132</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>517</v>
@@ -6722,7 +7923,7 @@
         <v>348</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1230</v>
+        <v>1254</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
@@ -6737,7 +7938,7 @@
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>1094</v>
+        <v>1120</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>133</v>
@@ -6746,7 +7947,7 @@
         <v>134</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1231</v>
+        <v>1255</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>521</v>
@@ -6761,7 +7962,7 @@
         <v>348</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1232</v>
+        <v>1256</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -6776,7 +7977,7 @@
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1094</v>
+        <v>1120</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>135</v>
@@ -6785,7 +7986,7 @@
         <v>136</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1233</v>
+        <v>1257</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>525</v>
@@ -6800,10 +8001,10 @@
         <v>337</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1234</v>
+        <v>1258</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>1235</v>
+        <v>1259</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>1008</v>
@@ -6817,7 +8018,7 @@
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>137</v>
@@ -6826,7 +8027,7 @@
         <v>138</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>531</v>
@@ -6841,7 +8042,7 @@
         <v>348</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1237</v>
+        <v>1261</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -6856,7 +8057,7 @@
     </row>
     <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>139</v>
@@ -6865,7 +8066,7 @@
         <v>140</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>535</v>
@@ -6880,10 +8081,10 @@
         <v>337</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>1240</v>
+        <v>1264</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>1008</v>
@@ -6897,7 +8098,7 @@
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>141</v>
@@ -6906,7 +8107,7 @@
         <v>142</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>541</v>
@@ -6921,10 +8122,10 @@
         <v>337</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1242</v>
+        <v>1266</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1243</v>
+        <v>1267</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1008</v>
@@ -6938,7 +8139,7 @@
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>143</v>
@@ -6947,7 +8148,7 @@
         <v>144</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1244</v>
+        <v>1268</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>547</v>
@@ -6962,7 +8163,7 @@
         <v>348</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1245</v>
+        <v>1269</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
@@ -6977,7 +8178,7 @@
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>145</v>
@@ -6986,7 +8187,7 @@
         <v>146</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1246</v>
+        <v>1270</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>551</v>
@@ -7001,7 +8202,7 @@
         <v>348</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1247</v>
+        <v>1271</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
@@ -7016,7 +8217,7 @@
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>147</v>
@@ -7025,7 +8226,7 @@
         <v>148</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1248</v>
+        <v>1272</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>555</v>
@@ -7040,7 +8241,7 @@
         <v>348</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
@@ -7055,7 +8256,7 @@
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>149</v>
@@ -7064,7 +8265,7 @@
         <v>150</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1250</v>
+        <v>1274</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>559</v>
@@ -7079,7 +8280,7 @@
         <v>348</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1251</v>
+        <v>1275</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -7094,7 +8295,7 @@
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1100</v>
+        <v>1126</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>151</v>
@@ -7103,7 +8304,7 @@
         <v>152</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1252</v>
+        <v>1276</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>563</v>
@@ -7118,10 +8319,10 @@
         <v>337</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1253</v>
+        <v>1277</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>1254</v>
+        <v>1278</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>1008</v>
@@ -7135,7 +8336,7 @@
     </row>
     <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>1100</v>
+        <v>1126</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>153</v>
@@ -7144,7 +8345,7 @@
         <v>154</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1255</v>
+        <v>1279</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>568</v>
@@ -7159,10 +8360,10 @@
         <v>337</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1256</v>
+        <v>1280</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>1257</v>
+        <v>1281</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>1008</v>
@@ -7176,7 +8377,7 @@
     </row>
     <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>1100</v>
+        <v>1126</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>155</v>
@@ -7185,7 +8386,7 @@
         <v>156</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1258</v>
+        <v>1282</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>574</v>
@@ -7200,10 +8401,10 @@
         <v>337</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1259</v>
+        <v>1283</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>1260</v>
+        <v>1284</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>1008</v>
@@ -7217,7 +8418,7 @@
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>1102</v>
+        <v>1128</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>159</v>
@@ -7226,7 +8427,7 @@
         <v>160</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1261</v>
+        <v>1285</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>576</v>
@@ -7241,7 +8442,7 @@
         <v>348</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
@@ -7256,7 +8457,7 @@
     </row>
     <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>1102</v>
+        <v>1128</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>161</v>
@@ -7265,7 +8466,7 @@
         <v>162</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1263</v>
+        <v>1287</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>580</v>
@@ -7280,10 +8481,10 @@
         <v>337</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1264</v>
+        <v>1288</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>1265</v>
+        <v>1289</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>1008</v>
@@ -7297,7 +8498,7 @@
     </row>
     <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>1102</v>
+        <v>1128</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>163</v>
@@ -7306,7 +8507,7 @@
         <v>164</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1266</v>
+        <v>1290</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>586</v>
@@ -7321,10 +8522,10 @@
         <v>337</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1267</v>
+        <v>1291</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1268</v>
+        <v>1292</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1008</v>
@@ -7338,7 +8539,7 @@
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>165</v>
@@ -7347,7 +8548,7 @@
         <v>166</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1269</v>
+        <v>1293</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>592</v>
@@ -7362,10 +8563,10 @@
         <v>337</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>1271</v>
+        <v>1295</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>1008</v>
@@ -7379,7 +8580,7 @@
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>167</v>
@@ -7388,7 +8589,7 @@
         <v>168</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1272</v>
+        <v>1296</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>598</v>
@@ -7403,7 +8604,7 @@
         <v>348</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1273</v>
+        <v>1297</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
@@ -7418,7 +8619,7 @@
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>169</v>
@@ -7427,7 +8628,7 @@
         <v>170</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1274</v>
+        <v>1298</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>602</v>
@@ -7442,7 +8643,7 @@
         <v>348</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1275</v>
+        <v>1299</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -7457,7 +8658,7 @@
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>171</v>
@@ -7466,7 +8667,7 @@
         <v>172</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1276</v>
+        <v>1300</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>606</v>
@@ -7481,7 +8682,7 @@
         <v>348</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1277</v>
+        <v>1301</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -7496,7 +8697,7 @@
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>173</v>
@@ -7505,7 +8706,7 @@
         <v>174</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1278</v>
+        <v>1302</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>610</v>
@@ -7520,7 +8721,7 @@
         <v>348</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1279</v>
+        <v>1303</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -7535,7 +8736,7 @@
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>1108</v>
+        <v>1134</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>175</v>
@@ -7544,7 +8745,7 @@
         <v>176</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1280</v>
+        <v>1304</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>614</v>
@@ -7559,7 +8760,7 @@
         <v>348</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1281</v>
+        <v>1305</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -7574,7 +8775,7 @@
     </row>
     <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>1108</v>
+        <v>1134</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>177</v>
@@ -7583,7 +8784,7 @@
         <v>178</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1282</v>
+        <v>1306</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>618</v>
@@ -7598,10 +8799,10 @@
         <v>337</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1283</v>
+        <v>1307</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1284</v>
+        <v>1308</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>1008</v>
@@ -7615,7 +8816,7 @@
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>1108</v>
+        <v>1134</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>179</v>
@@ -7624,7 +8825,7 @@
         <v>180</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1285</v>
+        <v>1309</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>625</v>
@@ -7639,10 +8840,10 @@
         <v>337</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1286</v>
+        <v>1310</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1287</v>
+        <v>1311</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1008</v>
@@ -7656,7 +8857,7 @@
     </row>
     <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>1108</v>
+        <v>1134</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>181</v>
@@ -7665,7 +8866,7 @@
         <v>182</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1288</v>
+        <v>1312</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>632</v>
@@ -7680,7 +8881,7 @@
         <v>348</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1289</v>
+        <v>1313</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
@@ -7695,7 +8896,7 @@
     </row>
     <row r="60" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>1110</v>
+        <v>1023</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>183</v>
@@ -7704,7 +8905,7 @@
         <v>184</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1290</v>
+        <v>1314</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>636</v>
@@ -7719,10 +8920,10 @@
         <v>337</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1291</v>
+        <v>1315</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1292</v>
+        <v>1316</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>1008</v>
@@ -7736,7 +8937,7 @@
     </row>
     <row r="61" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>1110</v>
+        <v>1023</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>185</v>
@@ -7745,7 +8946,7 @@
         <v>186</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1293</v>
+        <v>1317</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>642</v>
@@ -7760,7 +8961,7 @@
         <v>348</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1294</v>
+        <v>1318</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
@@ -7775,7 +8976,7 @@
     </row>
     <row r="62" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>1110</v>
+        <v>1023</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>187</v>
@@ -7784,7 +8985,7 @@
         <v>188</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1295</v>
+        <v>1319</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>646</v>
@@ -7799,7 +9000,7 @@
         <v>348</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1296</v>
+        <v>1320</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
@@ -7814,7 +9015,7 @@
     </row>
     <row r="63" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>1110</v>
+        <v>1023</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>189</v>
@@ -7823,7 +9024,7 @@
         <v>190</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1297</v>
+        <v>1321</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>650</v>
@@ -7838,7 +9039,7 @@
         <v>348</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1298</v>
+        <v>1322</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
@@ -7853,7 +9054,7 @@
     </row>
     <row r="64" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>1110</v>
+        <v>1023</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>191</v>
@@ -7862,7 +9063,7 @@
         <v>192</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1299</v>
+        <v>1323</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>654</v>
@@ -7877,7 +9078,7 @@
         <v>348</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1300</v>
+        <v>1324</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
@@ -7892,7 +9093,7 @@
     </row>
     <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>193</v>
@@ -7901,7 +9102,7 @@
         <v>194</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1301</v>
+        <v>1325</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>658</v>
@@ -7916,10 +9117,10 @@
         <v>337</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1302</v>
+        <v>1326</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>1303</v>
+        <v>1327</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>1008</v>
@@ -7933,7 +9134,7 @@
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>195</v>
@@ -7942,7 +9143,7 @@
         <v>196</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1304</v>
+        <v>1328</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>663</v>
@@ -7957,10 +9158,10 @@
         <v>337</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1305</v>
+        <v>1329</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1306</v>
+        <v>1330</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1008</v>
@@ -7974,7 +9175,7 @@
     </row>
     <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>197</v>
@@ -7983,7 +9184,7 @@
         <v>198</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1307</v>
+        <v>1331</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>670</v>
@@ -7998,10 +9199,10 @@
         <v>337</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1308</v>
+        <v>1332</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1309</v>
+        <v>1333</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1008</v>
@@ -8015,7 +9216,7 @@
     </row>
     <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>199</v>
@@ -8024,7 +9225,7 @@
         <v>200</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1310</v>
+        <v>1334</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>677</v>
@@ -8039,7 +9240,7 @@
         <v>348</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1311</v>
+        <v>1335</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
@@ -8054,7 +9255,7 @@
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>201</v>
@@ -8063,7 +9264,7 @@
         <v>202</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1312</v>
+        <v>1336</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>681</v>
@@ -8078,7 +9279,7 @@
         <v>348</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1313</v>
+        <v>1337</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
@@ -8093,7 +9294,7 @@
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>203</v>
@@ -8102,7 +9303,7 @@
         <v>204</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1314</v>
+        <v>1338</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>685</v>
@@ -8117,10 +9318,10 @@
         <v>337</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1315</v>
+        <v>1339</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>1316</v>
+        <v>1340</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>1008</v>
@@ -8134,7 +9335,7 @@
     </row>
     <row r="71" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>205</v>
@@ -8143,7 +9344,7 @@
         <v>206</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1317</v>
+        <v>1341</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>691</v>
@@ -8158,10 +9359,10 @@
         <v>337</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1318</v>
+        <v>1342</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>1319</v>
+        <v>1343</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>1008</v>
@@ -8175,7 +9376,7 @@
     </row>
     <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>205</v>
@@ -8184,7 +9385,7 @@
         <v>206</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1317</v>
+        <v>1341</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>698</v>
@@ -8199,10 +9400,10 @@
         <v>337</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1320</v>
+        <v>1344</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1319</v>
+        <v>1343</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1008</v>
@@ -8216,7 +9417,7 @@
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>207</v>
@@ -8225,7 +9426,7 @@
         <v>208</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1321</v>
+        <v>1345</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>704</v>
@@ -8240,7 +9441,7 @@
         <v>348</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1322</v>
+        <v>1346</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
@@ -8255,7 +9456,7 @@
     </row>
     <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>209</v>
@@ -8264,7 +9465,7 @@
         <v>210</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1323</v>
+        <v>1347</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>708</v>
@@ -8279,10 +9480,10 @@
         <v>337</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1324</v>
+        <v>1348</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1325</v>
+        <v>1349</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>1008</v>
@@ -8296,7 +9497,7 @@
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>209</v>
@@ -8305,7 +9506,7 @@
         <v>210</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1323</v>
+        <v>1347</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>715</v>
@@ -8320,10 +9521,10 @@
         <v>337</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1326</v>
+        <v>1350</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>1325</v>
+        <v>1349</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>1008</v>
@@ -8337,7 +9538,7 @@
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>209</v>
@@ -8346,7 +9547,7 @@
         <v>210</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1323</v>
+        <v>1347</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>721</v>
@@ -8361,10 +9562,10 @@
         <v>337</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>1327</v>
+        <v>1351</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>1325</v>
+        <v>1349</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>1008</v>
@@ -8378,7 +9579,7 @@
     </row>
     <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>211</v>
@@ -8387,7 +9588,7 @@
         <v>212</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1328</v>
+        <v>1352</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>727</v>
@@ -8402,10 +9603,10 @@
         <v>337</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>1329</v>
+        <v>1353</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>1330</v>
+        <v>1354</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>1008</v>
@@ -8419,7 +9620,7 @@
     </row>
     <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>213</v>
@@ -8428,7 +9629,7 @@
         <v>214</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1331</v>
+        <v>1355</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>734</v>
@@ -8443,7 +9644,7 @@
         <v>348</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1332</v>
+        <v>1356</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
@@ -8458,7 +9659,7 @@
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>215</v>
@@ -8467,7 +9668,7 @@
         <v>216</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1333</v>
+        <v>1357</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>738</v>
@@ -8482,7 +9683,7 @@
         <v>348</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1334</v>
+        <v>1358</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -8497,7 +9698,7 @@
     </row>
     <row r="80" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>217</v>
@@ -8506,7 +9707,7 @@
         <v>218</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1335</v>
+        <v>1359</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>742</v>
@@ -8521,10 +9722,10 @@
         <v>337</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1336</v>
+        <v>1360</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>1337</v>
+        <v>1361</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>1008</v>
@@ -8538,7 +9739,7 @@
     </row>
     <row r="81" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>219</v>
@@ -8547,7 +9748,7 @@
         <v>220</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1338</v>
+        <v>1362</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>748</v>
@@ -8562,10 +9763,10 @@
         <v>337</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1339</v>
+        <v>1363</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1340</v>
+        <v>1364</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1008</v>
@@ -8579,7 +9780,7 @@
     </row>
     <row r="82" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>221</v>
@@ -8588,7 +9789,7 @@
         <v>222</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1341</v>
+        <v>1365</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>754</v>
@@ -8603,10 +9804,10 @@
         <v>337</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>1343</v>
+        <v>1367</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>1008</v>
@@ -8620,7 +9821,7 @@
     </row>
     <row r="83" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>223</v>
@@ -8629,7 +9830,7 @@
         <v>224</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>760</v>
@@ -8644,7 +9845,7 @@
         <v>348</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
@@ -8659,7 +9860,7 @@
     </row>
     <row r="84" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>225</v>
@@ -8668,7 +9869,7 @@
         <v>226</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1346</v>
+        <v>1370</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>764</v>
@@ -8683,7 +9884,7 @@
         <v>348</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -8698,7 +9899,7 @@
     </row>
     <row r="85" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>227</v>
@@ -8707,7 +9908,7 @@
         <v>228</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1348</v>
+        <v>1372</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>768</v>
@@ -8722,7 +9923,7 @@
         <v>348</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1349</v>
+        <v>1373</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -8737,7 +9938,7 @@
     </row>
     <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>1120</v>
+        <v>1144</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>229</v>
@@ -8746,7 +9947,7 @@
         <v>230</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1350</v>
+        <v>1374</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>772</v>
@@ -8761,10 +9962,10 @@
         <v>337</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1351</v>
+        <v>1375</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>1352</v>
+        <v>1376</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>1008</v>
@@ -8778,7 +9979,7 @@
     </row>
     <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>1120</v>
+        <v>1144</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>231</v>
@@ -8787,7 +9988,7 @@
         <v>232</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1353</v>
+        <v>1377</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>778</v>
@@ -8802,10 +10003,10 @@
         <v>337</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1354</v>
+        <v>1378</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1355</v>
+        <v>1379</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1008</v>
@@ -8819,7 +10020,7 @@
     </row>
     <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>1120</v>
+        <v>1144</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>233</v>
@@ -8828,7 +10029,7 @@
         <v>234</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1356</v>
+        <v>1380</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>783</v>
@@ -8843,10 +10044,10 @@
         <v>337</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1357</v>
+        <v>1381</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>1358</v>
+        <v>1382</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>1008</v>
@@ -8860,7 +10061,7 @@
     </row>
     <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>1124</v>
+        <v>1148</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>235</v>
@@ -8869,7 +10070,7 @@
         <v>236</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1359</v>
+        <v>1383</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>789</v>
@@ -8884,10 +10085,10 @@
         <v>337</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1360</v>
+        <v>1384</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>1008</v>
@@ -8901,7 +10102,7 @@
     </row>
     <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>1124</v>
+        <v>1148</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>237</v>
@@ -8910,7 +10111,7 @@
         <v>238</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1362</v>
+        <v>1386</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>795</v>
@@ -8925,10 +10126,10 @@
         <v>337</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1363</v>
+        <v>1387</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>1364</v>
+        <v>1388</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>1008</v>
@@ -8942,7 +10143,7 @@
     </row>
     <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>1124</v>
+        <v>1148</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>241</v>
@@ -8951,7 +10152,7 @@
         <v>242</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1365</v>
+        <v>1389</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>797</v>
@@ -8966,7 +10167,7 @@
         <v>348</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1366</v>
+        <v>1390</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
@@ -8981,7 +10182,7 @@
     </row>
     <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>1124</v>
+        <v>1148</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>243</v>
@@ -8990,7 +10191,7 @@
         <v>244</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1367</v>
+        <v>1391</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>801</v>
@@ -9005,10 +10206,10 @@
         <v>337</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1368</v>
+        <v>1392</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>1369</v>
+        <v>1393</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>1008</v>
@@ -9022,7 +10223,7 @@
     </row>
     <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>245</v>
@@ -9031,7 +10232,7 @@
         <v>246</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1370</v>
+        <v>1394</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>803</v>
@@ -9046,7 +10247,7 @@
         <v>348</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1371</v>
+        <v>1395</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
@@ -9061,7 +10262,7 @@
     </row>
     <row r="94" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>247</v>
@@ -9070,7 +10271,7 @@
         <v>248</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1372</v>
+        <v>1396</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>807</v>
@@ -9085,10 +10286,10 @@
         <v>337</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1373</v>
+        <v>1397</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>1374</v>
+        <v>1398</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>1008</v>
@@ -9102,7 +10303,7 @@
     </row>
     <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>249</v>
@@ -9111,7 +10312,7 @@
         <v>250</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1375</v>
+        <v>1399</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>814</v>
@@ -9126,7 +10327,7 @@
         <v>348</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1376</v>
+        <v>1400</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -9141,7 +10342,7 @@
     </row>
     <row r="96" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>251</v>
@@ -9150,7 +10351,7 @@
         <v>252</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1377</v>
+        <v>1401</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>818</v>
@@ -9165,7 +10366,7 @@
         <v>348</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1378</v>
+        <v>1402</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -9180,7 +10381,7 @@
     </row>
     <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>253</v>
@@ -9189,7 +10390,7 @@
         <v>254</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1379</v>
+        <v>1403</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>822</v>
@@ -9204,7 +10405,7 @@
         <v>348</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1380</v>
+        <v>1404</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -9219,7 +10420,7 @@
     </row>
     <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>1128</v>
+        <v>1152</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>255</v>
@@ -9228,7 +10429,7 @@
         <v>256</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1381</v>
+        <v>1405</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>826</v>
@@ -9243,10 +10444,10 @@
         <v>337</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1382</v>
+        <v>1406</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>1383</v>
+        <v>1407</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>1008</v>
@@ -9260,7 +10461,7 @@
     </row>
     <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>1128</v>
+        <v>1152</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>257</v>
@@ -9269,7 +10470,7 @@
         <v>258</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1384</v>
+        <v>1408</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>832</v>
@@ -9284,7 +10485,7 @@
         <v>348</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1385</v>
+        <v>1409</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -9299,7 +10500,7 @@
     </row>
     <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>1128</v>
+        <v>1152</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>259</v>
@@ -9308,7 +10509,7 @@
         <v>260</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1386</v>
+        <v>1410</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>836</v>
@@ -9323,7 +10524,7 @@
         <v>348</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1387</v>
+        <v>1411</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -9338,7 +10539,7 @@
     </row>
     <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>1132</v>
+        <v>1156</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>261</v>
@@ -9347,7 +10548,7 @@
         <v>262</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1388</v>
+        <v>1412</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>840</v>
@@ -9362,7 +10563,7 @@
         <v>348</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1389</v>
+        <v>1413</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -9377,7 +10578,7 @@
     </row>
     <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>1132</v>
+        <v>1156</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>263</v>
@@ -9386,7 +10587,7 @@
         <v>264</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1390</v>
+        <v>1414</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>844</v>
@@ -9401,7 +10602,7 @@
         <v>348</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1391</v>
+        <v>1415</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
@@ -9416,7 +10617,7 @@
     </row>
     <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>1132</v>
+        <v>1156</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>265</v>
@@ -9425,7 +10626,7 @@
         <v>266</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1392</v>
+        <v>1416</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>848</v>
@@ -9440,7 +10641,7 @@
         <v>348</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1393</v>
+        <v>1417</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -9455,7 +10656,7 @@
     </row>
     <row r="104" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>1132</v>
+        <v>1156</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>267</v>
@@ -9464,7 +10665,7 @@
         <v>268</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1394</v>
+        <v>1418</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>852</v>
@@ -9479,10 +10680,10 @@
         <v>337</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1395</v>
+        <v>1419</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>1396</v>
+        <v>1420</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>1008</v>
@@ -9496,7 +10697,7 @@
     </row>
     <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>1132</v>
+        <v>1156</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>269</v>
@@ -9505,7 +10706,7 @@
         <v>270</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1397</v>
+        <v>1421</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>854</v>
@@ -9520,7 +10721,7 @@
         <v>348</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1398</v>
+        <v>1422</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -9535,7 +10736,7 @@
     </row>
     <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>271</v>
@@ -9544,7 +10745,7 @@
         <v>272</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1399</v>
+        <v>1423</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>858</v>
@@ -9559,10 +10760,10 @@
         <v>337</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1400</v>
+        <v>1424</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1401</v>
+        <v>1425</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1008</v>
@@ -9576,7 +10777,7 @@
     </row>
     <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>273</v>
@@ -9585,7 +10786,7 @@
         <v>274</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1402</v>
+        <v>1426</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>864</v>
@@ -9600,7 +10801,7 @@
         <v>348</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1403</v>
+        <v>1427</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2" t="s">
@@ -9615,7 +10816,7 @@
     </row>
     <row r="108" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>277</v>
@@ -9624,7 +10825,7 @@
         <v>278</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1404</v>
+        <v>1428</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>868</v>
@@ -9639,7 +10840,7 @@
         <v>348</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1405</v>
+        <v>1429</v>
       </c>
       <c r="J108" s="2"/>
       <c r="K108" s="2" t="s">
@@ -9654,7 +10855,7 @@
     </row>
     <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>279</v>
@@ -9663,7 +10864,7 @@
         <v>280</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1406</v>
+        <v>1430</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>872</v>
@@ -9678,7 +10879,7 @@
         <v>348</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1407</v>
+        <v>1431</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
@@ -9693,7 +10894,7 @@
     </row>
     <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>281</v>
@@ -9702,7 +10903,7 @@
         <v>282</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1408</v>
+        <v>1432</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>876</v>
@@ -9717,7 +10918,7 @@
         <v>348</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1409</v>
+        <v>1433</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2" t="s">
@@ -9732,7 +10933,7 @@
     </row>
     <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>1136</v>
+        <v>1160</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>285</v>
@@ -9741,7 +10942,7 @@
         <v>286</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1410</v>
+        <v>1434</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>880</v>
@@ -9756,7 +10957,7 @@
         <v>348</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1411</v>
+        <v>1435</v>
       </c>
       <c r="J111" s="2"/>
       <c r="K111" s="2" t="s">
@@ -9771,7 +10972,7 @@
     </row>
     <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>1136</v>
+        <v>1160</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>287</v>
@@ -9780,7 +10981,7 @@
         <v>288</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1412</v>
+        <v>1436</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>884</v>
@@ -9795,7 +10996,7 @@
         <v>348</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1413</v>
+        <v>1437</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2" t="s">
@@ -9810,7 +11011,7 @@
     </row>
     <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>1136</v>
+        <v>1160</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>289</v>
@@ -9819,7 +11020,7 @@
         <v>290</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1414</v>
+        <v>1438</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>888</v>
@@ -9834,10 +11035,10 @@
         <v>337</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1415</v>
+        <v>1439</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>1416</v>
+        <v>1440</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>1008</v>
@@ -9851,7 +11052,7 @@
     </row>
     <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>1138</v>
+        <v>1162</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>293</v>
@@ -9860,7 +11061,7 @@
         <v>294</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1417</v>
+        <v>1441</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>893</v>
@@ -9875,7 +11076,7 @@
         <v>348</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1418</v>
+        <v>1442</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
@@ -9890,7 +11091,7 @@
     </row>
     <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>1138</v>
+        <v>1162</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>295</v>
@@ -9899,7 +11100,7 @@
         <v>296</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1419</v>
+        <v>1443</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>897</v>
@@ -9914,7 +11115,7 @@
         <v>348</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1420</v>
+        <v>1444</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2" t="s">
@@ -9929,7 +11130,7 @@
     </row>
     <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>1138</v>
+        <v>1162</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>297</v>
@@ -9938,7 +11139,7 @@
         <v>298</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1421</v>
+        <v>1445</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>901</v>
@@ -9953,7 +11154,7 @@
         <v>348</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1422</v>
+        <v>1446</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
@@ -9968,7 +11169,7 @@
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1423</v>
+        <v>1132</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>299</v>
@@ -9977,7 +11178,7 @@
         <v>300</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1424</v>
+        <v>1447</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>905</v>
@@ -9992,10 +11193,10 @@
         <v>337</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1425</v>
+        <v>1448</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1426</v>
+        <v>1449</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1008</v>
@@ -10009,7 +11210,7 @@
     </row>
     <row r="118" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>1423</v>
+        <v>1023</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>301</v>
@@ -10018,7 +11219,7 @@
         <v>302</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1427</v>
+        <v>1450</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>911</v>
@@ -10033,10 +11234,10 @@
         <v>337</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1428</v>
+        <v>1451</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>1008</v>
@@ -10050,7 +11251,7 @@
     </row>
     <row r="119" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>1423</v>
+        <v>1023</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>301</v>
@@ -10059,7 +11260,7 @@
         <v>302</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1427</v>
+        <v>1450</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>918</v>
@@ -10074,16 +11275,16 @@
         <v>337</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1430</v>
+        <v>1453</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>339</v>
+        <v>1020</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>339</v>
@@ -10091,7 +11292,7 @@
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1431</v>
+        <v>1152</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>303</v>
@@ -10100,7 +11301,7 @@
         <v>304</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1432</v>
+        <v>1454</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>924</v>
@@ -10115,10 +11316,10 @@
         <v>337</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1434</v>
+        <v>1456</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>1008</v>
@@ -10132,7 +11333,7 @@
     </row>
     <row r="121" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>1435</v>
+        <v>1030</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>305</v>
@@ -10141,7 +11342,7 @@
         <v>306</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1436</v>
+        <v>1457</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>930</v>
@@ -10156,10 +11357,10 @@
         <v>337</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1437</v>
+        <v>1458</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1438</v>
+        <v>1459</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>1008</v>
@@ -10173,7 +11374,7 @@
     </row>
     <row r="122" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>1435</v>
+        <v>1030</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>305</v>
@@ -10182,7 +11383,7 @@
         <v>306</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1436</v>
+        <v>1457</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>936</v>
@@ -10197,16 +11398,16 @@
         <v>337</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1439</v>
+        <v>1460</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1438</v>
+        <v>1459</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>339</v>
+        <v>1028</v>
       </c>
       <c r="M122" s="2" t="s">
         <v>339</v>
@@ -10214,7 +11415,7 @@
     </row>
     <row r="123" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>1435</v>
+        <v>1030</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>305</v>
@@ -10223,7 +11424,7 @@
         <v>306</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1436</v>
+        <v>1457</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>940</v>
@@ -10238,10 +11439,10 @@
         <v>337</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1440</v>
+        <v>1461</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>1438</v>
+        <v>1459</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>1008</v>
@@ -10255,7 +11456,7 @@
     </row>
     <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>307</v>
@@ -10264,7 +11465,7 @@
         <v>308</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1442</v>
+        <v>1462</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>945</v>
@@ -10279,10 +11480,10 @@
         <v>337</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1443</v>
+        <v>1463</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1444</v>
+        <v>1464</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>1008</v>
@@ -10296,7 +11497,7 @@
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>307</v>
@@ -10305,7 +11506,7 @@
         <v>308</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1442</v>
+        <v>1462</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>952</v>
@@ -10320,10 +11521,10 @@
         <v>337</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1445</v>
+        <v>1465</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1444</v>
+        <v>1464</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1008</v>
@@ -10337,7 +11538,7 @@
     </row>
     <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>307</v>
@@ -10346,7 +11547,7 @@
         <v>308</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1442</v>
+        <v>1462</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>958</v>
@@ -10361,10 +11562,10 @@
         <v>337</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>1446</v>
+        <v>1466</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>1444</v>
+        <v>1464</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1008</v>
@@ -10378,7 +11579,7 @@
     </row>
     <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>307</v>
@@ -10387,7 +11588,7 @@
         <v>308</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1442</v>
+        <v>1462</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>963</v>
@@ -10402,10 +11603,10 @@
         <v>337</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1447</v>
+        <v>1467</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1444</v>
+        <v>1464</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>1008</v>
@@ -10419,7 +11620,7 @@
     </row>
     <row r="128" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>309</v>
@@ -10428,7 +11629,7 @@
         <v>310</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1448</v>
+        <v>1468</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>968</v>
@@ -10443,10 +11644,10 @@
         <v>337</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1449</v>
+        <v>1469</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1450</v>
+        <v>1470</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1008</v>
@@ -10460,7 +11661,7 @@
     </row>
     <row r="129" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>309</v>
@@ -10469,7 +11670,7 @@
         <v>310</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1448</v>
+        <v>1468</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>974</v>
@@ -10484,10 +11685,10 @@
         <v>337</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1451</v>
+        <v>1471</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1450</v>
+        <v>1470</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1008</v>
@@ -10501,7 +11702,7 @@
     </row>
     <row r="130" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>309</v>
@@ -10510,7 +11711,7 @@
         <v>310</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1448</v>
+        <v>1468</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>980</v>
@@ -10525,10 +11726,10 @@
         <v>337</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>1452</v>
+        <v>1472</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>1450</v>
+        <v>1470</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1008</v>
@@ -10542,7 +11743,7 @@
     </row>
     <row r="131" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>309</v>
@@ -10551,7 +11752,7 @@
         <v>310</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1448</v>
+        <v>1468</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>986</v>
@@ -10566,16 +11767,16 @@
         <v>337</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1453</v>
+        <v>1473</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1450</v>
+        <v>1470</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>339</v>
+        <v>1035</v>
       </c>
       <c r="M131" s="2" t="s">
         <v>339</v>
@@ -10583,7 +11784,7 @@
     </row>
     <row r="132" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>311</v>
@@ -10592,7 +11793,7 @@
         <v>312</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1454</v>
+        <v>1474</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>992</v>
@@ -10607,10 +11808,10 @@
         <v>337</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1455</v>
+        <v>1475</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1456</v>
+        <v>1476</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1008</v>
@@ -10624,7 +11825,7 @@
     </row>
     <row r="133" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>1441</v>
+        <v>1037</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>311</v>
@@ -10633,7 +11834,7 @@
         <v>312</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1454</v>
+        <v>1474</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>998</v>
@@ -10648,10 +11849,10 @@
         <v>337</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1457</v>
+        <v>1477</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1456</v>
+        <v>1476</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1008</v>
@@ -10669,7 +11870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -10683,36 +11884,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1458</v>
+        <v>1478</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1459</v>
+        <v>1479</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1460</v>
+        <v>1480</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1461</v>
+        <v>1481</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1462</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1463</v>
+        <v>1483</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1464</v>
+        <v>1484</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1465</v>
+        <v>1485</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1466</v>
+        <v>1486</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1467</v>
+        <v>1487</v>
       </c>
     </row>
   </sheetData>
@@ -10721,7 +11922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -10735,189 +11936,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1468</v>
+        <v>1488</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1469</v>
+        <v>1489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1470</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1471</v>
+        <v>1491</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1472</v>
+        <v>1492</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1473</v>
+        <v>1493</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1474</v>
+        <v>1494</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1475</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1476</v>
+        <v>1496</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1477</v>
+        <v>1497</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1478</v>
+        <v>1498</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1479</v>
+        <v>1499</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1480</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1481</v>
+        <v>1501</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1482</v>
+        <v>1502</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1483</v>
+        <v>1503</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1484</v>
+        <v>1504</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1485</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1486</v>
+        <v>1506</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1487</v>
+        <v>1507</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1488</v>
+        <v>1508</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1489</v>
+        <v>1509</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1490</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1491</v>
+        <v>1511</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1492</v>
+        <v>1512</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1493</v>
+        <v>1513</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1494</v>
+        <v>1514</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1495</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1496</v>
+        <v>1516</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1497</v>
+        <v>1517</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1498</v>
+        <v>1518</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1499</v>
+        <v>1519</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1500</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1501</v>
+        <v>1521</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1502</v>
+        <v>1522</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1503</v>
+        <v>1523</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1504</v>
+        <v>1524</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1505</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1506</v>
+        <v>1526</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1507</v>
+        <v>1527</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1508</v>
+        <v>1528</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1509</v>
+        <v>1529</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1510</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1511</v>
+        <v>1531</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1512</v>
+        <v>1532</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1513</v>
+        <v>1533</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1514</v>
+        <v>1534</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1515</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1516</v>
+        <v>1536</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1517</v>
+        <v>1537</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1518</v>
+        <v>1538</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1519</v>
+        <v>1539</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1520</v>
+        <v>1540</v>
       </c>
     </row>
   </sheetData>
@@ -10926,7 +12127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -10940,186 +12141,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1521</v>
+        <v>1541</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1522</v>
+        <v>1542</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1523</v>
+        <v>1543</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1524</v>
+        <v>1544</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1525</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1526</v>
+        <v>1546</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1527</v>
+        <v>1547</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1529</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1496</v>
+        <v>1516</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1530</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1516</v>
+        <v>1536</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1532</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1533</v>
+        <v>1553</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1534</v>
+        <v>1554</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1535</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1536</v>
+        <v>1556</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1537</v>
+        <v>1557</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1538</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1539</v>
+        <v>1559</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1540</v>
+        <v>1560</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1541</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1542</v>
+        <v>1562</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1544</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1545</v>
+        <v>1565</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1546</v>
+        <v>1566</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1547</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>1548</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>1549</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1528</v>
-      </c>
       <c r="D10" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1550</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1551</v>
+        <v>1571</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1552</v>
+        <v>1572</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1553</v>
+        <v>1573</v>
       </c>
     </row>
   </sheetData>
@@ -19882,7 +21083,7 @@
         <v>1008</v>
       </c>
       <c r="E2" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -20000,7 +21201,7 @@
         <v>1008</v>
       </c>
       <c r="E8" s="2">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -20018,7 +21219,7 @@
         <v>1008</v>
       </c>
       <c r="E9" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -20036,7 +21237,7 @@
         <v>1008</v>
       </c>
       <c r="E10" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -20054,7 +21255,7 @@
         <v>1008</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -20072,7 +21273,7 @@
         <v>1008</v>
       </c>
       <c r="E12" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -20090,7 +21291,7 @@
         <v>1008</v>
       </c>
       <c r="E13" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -20168,7 +21369,7 @@
         <v>1008</v>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -20186,7 +21387,7 @@
         <v>1008</v>
       </c>
       <c r="E18" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -20244,7 +21445,7 @@
         <v>1008</v>
       </c>
       <c r="E21" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -20282,7 +21483,7 @@
         <v>1008</v>
       </c>
       <c r="E23" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -20300,7 +21501,7 @@
         <v>1008</v>
       </c>
       <c r="E24" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -20336,7 +21537,7 @@
         <v>1008</v>
       </c>
       <c r="E26" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -20354,7 +21555,7 @@
         <v>1008</v>
       </c>
       <c r="E27" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -20390,7 +21591,7 @@
         <v>1008</v>
       </c>
       <c r="E29" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -20408,7 +21609,7 @@
         <v>1008</v>
       </c>
       <c r="E30" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -20426,7 +21627,7 @@
         <v>1008</v>
       </c>
       <c r="E31" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -20464,7 +21665,7 @@
         <v>1008</v>
       </c>
       <c r="E33" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -20482,7 +21683,7 @@
         <v>1008</v>
       </c>
       <c r="E34" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -20540,7 +21741,7 @@
         <v>1008</v>
       </c>
       <c r="E37" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -20578,7 +21779,7 @@
         <v>1008</v>
       </c>
       <c r="E39" s="2">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -20596,7 +21797,7 @@
         <v>1008</v>
       </c>
       <c r="E40" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -20694,7 +21895,7 @@
         <v>1008</v>
       </c>
       <c r="E45" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -20712,7 +21913,7 @@
         <v>1008</v>
       </c>
       <c r="E46" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -20730,7 +21931,7 @@
         <v>1008</v>
       </c>
       <c r="E47" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -20768,7 +21969,7 @@
         <v>1008</v>
       </c>
       <c r="E49" s="2">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -20786,7 +21987,7 @@
         <v>1008</v>
       </c>
       <c r="E50" s="2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -20804,7 +22005,7 @@
         <v>1008</v>
       </c>
       <c r="E51" s="2">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -20922,7 +22123,7 @@
         <v>1008</v>
       </c>
       <c r="E57" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -20940,7 +22141,7 @@
         <v>1008</v>
       </c>
       <c r="E58" s="2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -20978,7 +22179,7 @@
         <v>1008</v>
       </c>
       <c r="E60" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -21076,7 +22277,7 @@
         <v>1008</v>
       </c>
       <c r="E65" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -21094,7 +22295,7 @@
         <v>1008</v>
       </c>
       <c r="E66" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -21112,7 +22313,7 @@
         <v>1008</v>
       </c>
       <c r="E67" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -21170,7 +22371,7 @@
         <v>1008</v>
       </c>
       <c r="E70" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -21188,7 +22389,7 @@
         <v>1008</v>
       </c>
       <c r="E71" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -21206,7 +22407,7 @@
         <v>1008</v>
       </c>
       <c r="E72" s="2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -21244,7 +22445,7 @@
         <v>1008</v>
       </c>
       <c r="E74" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -21262,7 +22463,7 @@
         <v>1008</v>
       </c>
       <c r="E75" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -21280,7 +22481,7 @@
         <v>1008</v>
       </c>
       <c r="E76" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -21298,7 +22499,7 @@
         <v>1008</v>
       </c>
       <c r="E77" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -21356,7 +22557,7 @@
         <v>1008</v>
       </c>
       <c r="E80" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -21374,7 +22575,7 @@
         <v>1008</v>
       </c>
       <c r="E81" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -21392,7 +22593,7 @@
         <v>1008</v>
       </c>
       <c r="E82" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -21470,7 +22671,7 @@
         <v>1008</v>
       </c>
       <c r="E86" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -21506,7 +22707,7 @@
         <v>1008</v>
       </c>
       <c r="E88" s="2">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -21524,7 +22725,7 @@
         <v>1008</v>
       </c>
       <c r="E89" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -21542,7 +22743,7 @@
         <v>1008</v>
       </c>
       <c r="E90" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -21580,7 +22781,7 @@
         <v>1008</v>
       </c>
       <c r="E92" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -21618,7 +22819,7 @@
         <v>1008</v>
       </c>
       <c r="E94" s="2">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -21696,7 +22897,7 @@
         <v>1008</v>
       </c>
       <c r="E98" s="2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -21852,7 +23053,7 @@
         <v>1008</v>
       </c>
       <c r="E106" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -21990,7 +23191,7 @@
         <v>1008</v>
       </c>
       <c r="E113" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -22068,7 +23269,7 @@
         <v>1008</v>
       </c>
       <c r="E117" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -22086,7 +23287,7 @@
         <v>1008</v>
       </c>
       <c r="E118" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -22101,10 +23302,10 @@
         <v>919</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="E119" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -22122,7 +23323,7 @@
         <v>1008</v>
       </c>
       <c r="E120" s="2">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -22140,7 +23341,7 @@
         <v>1008</v>
       </c>
       <c r="E121" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -22155,10 +23356,10 @@
         <v>937</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="E122" s="2">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -22176,7 +23377,7 @@
         <v>1008</v>
       </c>
       <c r="E123" s="2">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -22194,7 +23395,7 @@
         <v>1008</v>
       </c>
       <c r="E124" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -22212,7 +23413,7 @@
         <v>1008</v>
       </c>
       <c r="E125" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -22230,7 +23431,7 @@
         <v>1008</v>
       </c>
       <c r="E126" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -22248,7 +23449,7 @@
         <v>1008</v>
       </c>
       <c r="E127" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -22266,7 +23467,7 @@
         <v>1008</v>
       </c>
       <c r="E128" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -22284,7 +23485,7 @@
         <v>1008</v>
       </c>
       <c r="E129" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -22302,7 +23503,7 @@
         <v>1008</v>
       </c>
       <c r="E130" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -22317,10 +23518,10 @@
         <v>987</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="E131" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -22338,7 +23539,7 @@
         <v>1008</v>
       </c>
       <c r="E132" s="2">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -22356,7 +23557,7 @@
         <v>1008</v>
       </c>
       <c r="E133" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -22368,7 +23569,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -22386,16 +23587,16 @@
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1004</v>
@@ -22404,16 +23605,121 @@
         <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -22423,6 +23729,53 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="11" customWidth="1"/>
+    <col min="9" max="9" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -22440,16 +23793,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1019</v>
+        <v>1043</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1020</v>
+        <v>1044</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1021</v>
+        <v>1045</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -22478,7 +23831,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22501,7 +23854,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22524,7 +23877,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22547,7 +23900,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22570,7 +23923,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22593,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22616,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22639,7 +23992,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22662,7 +24015,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22685,7 +24038,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22708,7 +24061,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22731,7 +24084,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22754,7 +24107,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22777,7 +24130,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22800,7 +24153,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22823,7 +24176,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22846,7 +24199,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22869,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22892,7 +24245,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22915,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22938,7 +24291,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22961,7 +24314,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22984,7 +24337,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23007,7 +24360,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23030,7 +24383,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23053,7 +24406,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23076,7 +24429,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23099,7 +24452,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23122,7 +24475,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23145,7 +24498,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23168,7 +24521,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23191,7 +24544,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23214,7 +24567,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23237,7 +24590,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23260,7 +24613,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23283,7 +24636,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23306,7 +24659,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23329,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23352,7 +24705,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23375,7 +24728,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23398,7 +24751,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23421,7 +24774,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23444,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23467,7 +24820,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23490,7 +24843,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23513,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23536,7 +24889,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23559,7 +24912,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23582,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23605,7 +24958,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23628,7 +24981,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23651,7 +25004,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23674,7 +25027,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23697,7 +25050,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23720,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23743,7 +25096,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23766,7 +25119,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23789,7 +25142,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23812,7 +25165,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23835,7 +25188,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23858,7 +25211,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23881,7 +25234,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23904,7 +25257,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23927,7 +25280,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23950,7 +25303,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23973,7 +25326,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23996,7 +25349,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24019,7 +25372,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24042,7 +25395,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24065,7 +25418,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24088,7 +25441,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24111,7 +25464,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24134,7 +25487,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24157,7 +25510,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24180,7 +25533,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24203,7 +25556,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24226,7 +25579,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24249,7 +25602,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24272,7 +25625,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24295,7 +25648,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24318,7 +25671,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24341,7 +25694,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24364,7 +25717,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24387,7 +25740,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24410,7 +25763,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24433,7 +25786,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24456,7 +25809,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24479,7 +25832,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24502,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24525,7 +25878,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24548,7 +25901,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24571,7 +25924,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24594,7 +25947,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24617,7 +25970,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24640,7 +25993,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24663,7 +26016,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24686,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24709,7 +26062,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24732,7 +26085,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24755,7 +26108,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24778,7 +26131,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24801,7 +26154,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24824,7 +26177,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24847,7 +26200,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24870,7 +26223,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24893,7 +26246,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24916,7 +26269,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24939,7 +26292,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24962,7 +26315,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24985,7 +26338,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25008,7 +26361,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25031,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25054,7 +26407,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25077,7 +26430,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25100,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25123,7 +26476,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25146,7 +26499,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25169,7 +26522,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25192,7 +26545,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25215,7 +26568,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25238,7 +26591,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25261,7 +26614,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25281,10 +26634,10 @@
         <v>2</v>
       </c>
       <c r="F124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1023</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25307,7 +26660,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25327,10 +26680,10 @@
         <v>3</v>
       </c>
       <c r="F126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1023</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25353,7 +26706,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25373,10 +26726,10 @@
         <v>4</v>
       </c>
       <c r="F128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1023</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25399,7 +26752,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>
@@ -25408,7 +26761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -25421,13 +26774,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1027</v>
+        <v>1052</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -25435,1352 +26788,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1028</v>
+        <v>1053</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1029</v>
+        <v>1054</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1032</v>
+        <v>1057</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1033</v>
+        <v>1058</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1035</v>
+        <v>1060</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1036</v>
+        <v>1061</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1037</v>
+        <v>1062</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1039</v>
+        <v>1064</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1040</v>
+        <v>1065</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1031</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1041</v>
+        <v>1067</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1042</v>
+        <v>1068</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1043</v>
+        <v>1069</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1031</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1044</v>
+        <v>1070</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1045</v>
+        <v>1071</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>980</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1047</v>
+        <v>1073</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1048</v>
+        <v>1074</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1049</v>
+        <v>1075</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1050</v>
+        <v>1076</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1051</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1052</v>
+        <v>1078</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1053</v>
+        <v>1079</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1054</v>
+        <v>1080</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1031</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1055</v>
+        <v>1081</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1058</v>
+        <v>1084</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1059</v>
+        <v>1085</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>618</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1060</v>
+        <v>1086</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1061</v>
+        <v>1087</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1062</v>
+        <v>1088</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1063</v>
+        <v>1089</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1064</v>
+        <v>1090</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1065</v>
+        <v>1091</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1066</v>
+        <v>1092</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1067</v>
+        <v>1093</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>670</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1068</v>
+        <v>1094</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1069</v>
+        <v>1095</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E4" s="2">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2">
-        <v>6</v>
-      </c>
-      <c r="H4" s="2">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2">
-        <v>4</v>
-      </c>
-      <c r="G5" s="2">
-        <v>2</v>
-      </c>
-      <c r="H5" s="2">
-        <v>2</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3</v>
-      </c>
-      <c r="G6" s="2">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2">
-        <v>4</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2">
-        <v>5</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5</v>
-      </c>
-      <c r="H8" s="2">
-        <v>5</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E9" s="2">
-        <v>4</v>
-      </c>
-      <c r="F9" s="2">
-        <v>5</v>
-      </c>
-      <c r="G9" s="2">
-        <v>4</v>
-      </c>
-      <c r="H9" s="2">
-        <v>4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2">
-        <v>4</v>
-      </c>
-      <c r="G10" s="2">
-        <v>2</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E11" s="2">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2">
-        <v>4</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E12" s="2">
-        <v>7</v>
-      </c>
-      <c r="F12" s="2">
-        <v>7</v>
-      </c>
-      <c r="G12" s="2">
-        <v>2</v>
-      </c>
-      <c r="H12" s="2">
-        <v>2</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E13" s="2">
-        <v>3</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2">
-        <v>3</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E14" s="2">
-        <v>3</v>
-      </c>
-      <c r="F14" s="2">
-        <v>3</v>
-      </c>
-      <c r="G14" s="2">
-        <v>2</v>
-      </c>
-      <c r="H14" s="2">
-        <v>2</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E16" s="2">
-        <v>5</v>
-      </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E17" s="2">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2">
-        <v>4</v>
-      </c>
-      <c r="G17" s="2">
-        <v>2</v>
-      </c>
-      <c r="H17" s="2">
-        <v>2</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E18" s="2">
-        <v>5</v>
-      </c>
-      <c r="F18" s="2">
-        <v>5</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E19" s="2">
-        <v>4</v>
-      </c>
-      <c r="F19" s="2">
-        <v>4</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E20" s="2">
-        <v>6</v>
-      </c>
-      <c r="F20" s="2">
-        <v>6</v>
-      </c>
-      <c r="G20" s="2">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2">
-        <v>4</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E21" s="2">
-        <v>6</v>
-      </c>
-      <c r="F21" s="2">
-        <v>9</v>
-      </c>
-      <c r="G21" s="2">
-        <v>6</v>
-      </c>
-      <c r="H21" s="2">
-        <v>6</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E22" s="2">
-        <v>6</v>
-      </c>
-      <c r="F22" s="2">
-        <v>6</v>
-      </c>
-      <c r="G22" s="2">
-        <v>3</v>
-      </c>
-      <c r="H22" s="2">
-        <v>3</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E23" s="2">
-        <v>3</v>
-      </c>
-      <c r="F23" s="2">
-        <v>3</v>
-      </c>
-      <c r="G23" s="2">
-        <v>3</v>
-      </c>
-      <c r="H23" s="2">
-        <v>3</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E24" s="2">
-        <v>4</v>
-      </c>
-      <c r="F24" s="2">
-        <v>4</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E25" s="2">
-        <v>4</v>
-      </c>
-      <c r="F25" s="2">
-        <v>4</v>
-      </c>
-      <c r="G25" s="2">
-        <v>3</v>
-      </c>
-      <c r="H25" s="2">
-        <v>3</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E26" s="2">
-        <v>5</v>
-      </c>
-      <c r="F26" s="2">
-        <v>5</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E27" s="2">
-        <v>3</v>
-      </c>
-      <c r="F27" s="2">
-        <v>3</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E28" s="2">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2">
-        <v>4</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
-      </c>
-      <c r="F29" s="2">
-        <v>5</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E30" s="2">
-        <v>5</v>
-      </c>
-      <c r="F30" s="2">
-        <v>5</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2">
-        <v>1</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E31" s="2">
-        <v>3</v>
-      </c>
-      <c r="F31" s="2">
-        <v>3</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2">
-        <v>1</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E32" s="2">
-        <v>3</v>
-      </c>
-      <c r="F32" s="2">
-        <v>3</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>1080</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5650" uniqueCount="1574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5682" uniqueCount="1576">
   <si>
     <t>Metric</t>
   </si>
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:04:42.395Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:25:46.538Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3373,6 +3373,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>Scope</t>
+  </si>
+  <si>
     <t>Parent</t>
   </si>
   <si>
@@ -3382,6 +3385,9 @@
     <t>initiative</t>
   </si>
   <si>
+    <t>this cycle</t>
+  </si>
+  <si>
     <t>[Initiative] Intelligent Hotel Shopping and Reservation Experience</t>
   </si>
   <si>
@@ -4537,7 +4543,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T20:04:43.242Z</t>
+    <t>2026-10-02T20:25:47.603Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5371,19 +5377,19 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="1" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1096</v>
       </c>
@@ -5397,83 +5403,89 @@
         <v>1099</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>339</v>
+        <v>1102</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2</v>
+        <v>339</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1103</v>
       </c>
       <c r="F2" s="2">
         <v>2</v>
       </c>
       <c r="G2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4</v>
+      <c r="E3" s="2" t="s">
+        <v>1107</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
       </c>
       <c r="G3" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -5481,139 +5493,151 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>339</v>
+      <c r="J3" s="2">
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E4" s="2">
+        <v>1105</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F4" s="2">
         <v>7</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>9</v>
-      </c>
-      <c r="G4" s="2">
-        <v>6</v>
       </c>
       <c r="H4" s="2">
         <v>6</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>339</v>
+        <v>6</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1037</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F5" s="2">
+        <v>7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2">
+        <v>11</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="E5" s="2">
-        <v>7</v>
-      </c>
-      <c r="F5" s="2">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2">
-        <v>12</v>
-      </c>
-      <c r="H5" s="2">
-        <v>11</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1108</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3</v>
+        <v>1105</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1115</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2">
         <v>2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4</v>
+      <c r="E7" s="2" t="s">
+        <v>1117</v>
       </c>
       <c r="F7" s="2">
         <v>4</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -5621,28 +5645,31 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>339</v>
+      <c r="J7" s="2">
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
+      <c r="E8" s="2" t="s">
+        <v>1119</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -5654,106 +5681,115 @@
         <v>5</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>339</v>
+        <v>5</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1114</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E9" s="2">
+        <v>1116</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F9" s="2">
         <v>4</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>5</v>
-      </c>
-      <c r="G9" s="2">
-        <v>4</v>
       </c>
       <c r="H9" s="2">
         <v>4</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>339</v>
+        <v>4</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1114</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4</v>
+        <v>1116</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1123</v>
       </c>
       <c r="F10" s="2">
         <v>4</v>
       </c>
       <c r="G10" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2">
         <v>2</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E11" s="2">
-        <v>4</v>
+      <c r="E11" s="2" t="s">
+        <v>1125</v>
       </c>
       <c r="F11" s="2">
         <v>4</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -5761,63 +5797,69 @@
       <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>339</v>
+      <c r="J11" s="2">
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E12" s="2">
-        <v>7</v>
+      <c r="E12" s="2" t="s">
+        <v>1127</v>
       </c>
       <c r="F12" s="2">
         <v>7</v>
       </c>
       <c r="G12" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H12" s="2">
         <v>2</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1122</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E13" s="2">
-        <v>3</v>
+        <v>1124</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1129</v>
       </c>
       <c r="F13" s="2">
         <v>3</v>
@@ -5829,71 +5871,77 @@
         <v>3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>339</v>
+        <v>3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1122</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E14" s="2">
-        <v>3</v>
+        <v>1124</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1131</v>
       </c>
       <c r="F14" s="2">
         <v>3</v>
       </c>
       <c r="G14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2">
         <v>2</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4</v>
+      <c r="E15" s="2" t="s">
+        <v>1133</v>
       </c>
       <c r="F15" s="2">
         <v>4</v>
       </c>
       <c r="G15" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -5901,139 +5949,151 @@
       <c r="I15" s="2">
         <v>0</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>339</v>
+      <c r="J15" s="2">
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E16" s="2">
-        <v>6</v>
+      <c r="E16" s="2" t="s">
+        <v>1135</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2">
         <v>2</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1130</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E17" s="2">
-        <v>4</v>
+        <v>1132</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1137</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
       </c>
       <c r="G17" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="2">
         <v>2</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>1023</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1130</v>
+        <v>1102</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="E18" s="2">
+        <v>1132</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F18" s="2">
         <v>6</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>7</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>3</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>2</v>
       </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L18" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="E19" s="2">
-        <v>4</v>
+      <c r="E19" s="2" t="s">
+        <v>1140</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -6041,133 +6101,145 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>339</v>
+      <c r="J19" s="2">
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>1140</v>
-      </c>
-      <c r="E20" s="2">
-        <v>6</v>
+      <c r="E20" s="2" t="s">
+        <v>1142</v>
       </c>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2">
         <v>4</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>339</v>
+        <v>4</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1137</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="E21" s="2">
+        <v>1139</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F21" s="2">
         <v>6</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>9</v>
-      </c>
-      <c r="G21" s="2">
-        <v>6</v>
       </c>
       <c r="H21" s="2">
         <v>6</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>339</v>
+        <v>6</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>1030</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1137</v>
+        <v>1102</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E22" s="2">
+        <v>1139</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F22" s="2">
         <v>7</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <v>9</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <v>6</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>5</v>
       </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L22" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1137</v>
+        <v>1102</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E23" s="2">
-        <v>3</v>
+        <v>1139</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1147</v>
       </c>
       <c r="F23" s="2">
         <v>3</v>
@@ -6179,36 +6251,39 @@
         <v>3</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>339</v>
+        <v>3</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E24" s="2">
-        <v>4</v>
+      <c r="E24" s="2" t="s">
+        <v>1149</v>
       </c>
       <c r="F24" s="2">
         <v>4</v>
       </c>
       <c r="G24" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
@@ -6216,139 +6291,151 @@
       <c r="I24" s="2">
         <v>0</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>339</v>
+      <c r="J24" s="2">
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="E25" s="2">
-        <v>4</v>
+      <c r="E25" s="2" t="s">
+        <v>1151</v>
       </c>
       <c r="F25" s="2">
         <v>4</v>
       </c>
       <c r="G25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="2">
         <v>3</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>339</v>
+        <v>3</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1146</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E26" s="2">
-        <v>5</v>
+        <v>1148</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1153</v>
       </c>
       <c r="F26" s="2">
         <v>5</v>
       </c>
       <c r="G26" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1146</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E27" s="2">
-        <v>4</v>
+        <v>1148</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1155</v>
       </c>
       <c r="F27" s="2">
         <v>4</v>
       </c>
       <c r="G27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="2">
         <v>2</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>339</v>
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
       </c>
       <c r="K27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E28" s="2">
-        <v>4</v>
+      <c r="E28" s="2" t="s">
+        <v>1157</v>
       </c>
       <c r="F28" s="2">
         <v>4</v>
       </c>
       <c r="G28" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
@@ -6356,139 +6443,151 @@
       <c r="I28" s="2">
         <v>0</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>339</v>
+      <c r="J28" s="2">
+        <v>0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
+      <c r="E29" s="2" t="s">
+        <v>1159</v>
       </c>
       <c r="F29" s="2">
         <v>5</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
       </c>
       <c r="K29" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>1154</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E30" s="2">
-        <v>5</v>
+        <v>1156</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1161</v>
       </c>
       <c r="F30" s="2">
         <v>5</v>
       </c>
       <c r="G30" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
       </c>
       <c r="K30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1154</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>1161</v>
-      </c>
-      <c r="E31" s="2">
-        <v>3</v>
+        <v>1156</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1163</v>
       </c>
       <c r="F31" s="2">
         <v>3</v>
       </c>
       <c r="G31" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>339</v>
+        <v>1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
       </c>
       <c r="K31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1154</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E32" s="2">
-        <v>3</v>
+        <v>1156</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1165</v>
       </c>
       <c r="F32" s="2">
         <v>3</v>
       </c>
       <c r="G32" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -6496,11 +6595,14 @@
       <c r="I32" s="2">
         <v>0</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>339</v>
+      <c r="J32" s="2">
+        <v>0</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1106</v>
+        <v>339</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>1108</v>
       </c>
     </row>
   </sheetData>
@@ -6529,19 +6631,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>314</v>
@@ -6550,19 +6652,19 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1005</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1015</v>
@@ -6579,7 +6681,7 @@
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>326</v>
@@ -6594,10 +6696,10 @@
         <v>337</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1008</v>
@@ -6620,7 +6722,7 @@
         <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>340</v>
@@ -6635,7 +6737,7 @@
         <v>348</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -6659,7 +6761,7 @@
         <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>349</v>
@@ -6674,7 +6776,7 @@
         <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -6698,7 +6800,7 @@
         <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>353</v>
@@ -6713,7 +6815,7 @@
         <v>348</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -6737,7 +6839,7 @@
         <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>357</v>
@@ -6752,7 +6854,7 @@
         <v>348</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -6776,7 +6878,7 @@
         <v>79</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>361</v>
@@ -6791,7 +6893,7 @@
         <v>348</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -6806,7 +6908,7 @@
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>80</v>
@@ -6815,7 +6917,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>365</v>
@@ -6830,10 +6932,10 @@
         <v>337</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1008</v>
@@ -6847,7 +6949,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>82</v>
@@ -6856,7 +6958,7 @@
         <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>373</v>
@@ -6871,10 +6973,10 @@
         <v>337</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1008</v>
@@ -6888,7 +6990,7 @@
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>84</v>
@@ -6897,7 +6999,7 @@
         <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>379</v>
@@ -6912,10 +7014,10 @@
         <v>337</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1008</v>
@@ -6929,7 +7031,7 @@
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>84</v>
@@ -6938,7 +7040,7 @@
         <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>386</v>
@@ -6953,10 +7055,10 @@
         <v>337</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1008</v>
@@ -6970,7 +7072,7 @@
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>84</v>
@@ -6979,7 +7081,7 @@
         <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>392</v>
@@ -6994,10 +7096,10 @@
         <v>337</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>1195</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>1193</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1008</v>
@@ -7011,7 +7113,7 @@
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>86</v>
@@ -7020,7 +7122,7 @@
         <v>87</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>398</v>
@@ -7035,10 +7137,10 @@
         <v>337</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1008</v>
@@ -7052,7 +7154,7 @@
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>89</v>
@@ -7061,7 +7163,7 @@
         <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>407</v>
@@ -7076,7 +7178,7 @@
         <v>348</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -7091,7 +7193,7 @@
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -7100,7 +7202,7 @@
         <v>92</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>411</v>
@@ -7115,7 +7217,7 @@
         <v>348</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -7130,7 +7232,7 @@
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>93</v>
@@ -7139,7 +7241,7 @@
         <v>94</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>415</v>
@@ -7154,7 +7256,7 @@
         <v>348</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -7178,7 +7280,7 @@
         <v>96</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>419</v>
@@ -7193,10 +7295,10 @@
         <v>337</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1008</v>
@@ -7219,7 +7321,7 @@
         <v>98</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>425</v>
@@ -7234,10 +7336,10 @@
         <v>337</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1008</v>
@@ -7260,7 +7362,7 @@
         <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>432</v>
@@ -7275,7 +7377,7 @@
         <v>348</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -7299,7 +7401,7 @@
         <v>104</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>436</v>
@@ -7314,7 +7416,7 @@
         <v>348</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -7329,7 +7431,7 @@
     </row>
     <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>105</v>
@@ -7338,7 +7440,7 @@
         <v>106</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>440</v>
@@ -7353,10 +7455,10 @@
         <v>337</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>1008</v>
@@ -7370,7 +7472,7 @@
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>107</v>
@@ -7379,7 +7481,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>442</v>
@@ -7394,7 +7496,7 @@
         <v>348</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
@@ -7409,7 +7511,7 @@
     </row>
     <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>109</v>
@@ -7418,7 +7520,7 @@
         <v>110</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>446</v>
@@ -7433,10 +7535,10 @@
         <v>337</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>1008</v>
@@ -7450,7 +7552,7 @@
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>111</v>
@@ -7459,7 +7561,7 @@
         <v>112</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>452</v>
@@ -7474,10 +7576,10 @@
         <v>337</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1008</v>
@@ -7491,7 +7593,7 @@
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>113</v>
@@ -7500,7 +7602,7 @@
         <v>114</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>458</v>
@@ -7515,10 +7617,10 @@
         <v>337</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1008</v>
@@ -7532,7 +7634,7 @@
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>115</v>
@@ -7541,7 +7643,7 @@
         <v>116</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>463</v>
@@ -7556,10 +7658,10 @@
         <v>337</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1008</v>
@@ -7573,7 +7675,7 @@
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>117</v>
@@ -7582,7 +7684,7 @@
         <v>118</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>471</v>
@@ -7597,10 +7699,10 @@
         <v>337</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1008</v>
@@ -7614,7 +7716,7 @@
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>119</v>
@@ -7623,7 +7725,7 @@
         <v>120</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>477</v>
@@ -7638,10 +7740,10 @@
         <v>337</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1008</v>
@@ -7655,7 +7757,7 @@
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>121</v>
@@ -7664,7 +7766,7 @@
         <v>122</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>484</v>
@@ -7679,10 +7781,10 @@
         <v>337</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1008</v>
@@ -7696,7 +7798,7 @@
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>123</v>
@@ -7705,7 +7807,7 @@
         <v>124</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>490</v>
@@ -7720,10 +7822,10 @@
         <v>337</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>1008</v>
@@ -7737,7 +7839,7 @@
     </row>
     <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>123</v>
@@ -7746,7 +7848,7 @@
         <v>124</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>496</v>
@@ -7761,10 +7863,10 @@
         <v>337</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>1008</v>
@@ -7778,7 +7880,7 @@
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>125</v>
@@ -7787,7 +7889,7 @@
         <v>126</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>501</v>
@@ -7802,7 +7904,7 @@
         <v>348</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
@@ -7817,7 +7919,7 @@
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>127</v>
@@ -7826,7 +7928,7 @@
         <v>128</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>505</v>
@@ -7841,10 +7943,10 @@
         <v>337</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>1008</v>
@@ -7858,7 +7960,7 @@
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>129</v>
@@ -7867,7 +7969,7 @@
         <v>130</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>511</v>
@@ -7882,10 +7984,10 @@
         <v>337</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1008</v>
@@ -7899,7 +8001,7 @@
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>131</v>
@@ -7908,7 +8010,7 @@
         <v>132</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>517</v>
@@ -7923,7 +8025,7 @@
         <v>348</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
@@ -7938,7 +8040,7 @@
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>133</v>
@@ -7947,7 +8049,7 @@
         <v>134</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>521</v>
@@ -7962,7 +8064,7 @@
         <v>348</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -7977,7 +8079,7 @@
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>135</v>
@@ -7986,7 +8088,7 @@
         <v>136</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>525</v>
@@ -8001,10 +8103,10 @@
         <v>337</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>1008</v>
@@ -8018,7 +8120,7 @@
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>137</v>
@@ -8027,7 +8129,7 @@
         <v>138</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>531</v>
@@ -8042,7 +8144,7 @@
         <v>348</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -8057,7 +8159,7 @@
     </row>
     <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>139</v>
@@ -8066,7 +8168,7 @@
         <v>140</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>535</v>
@@ -8081,10 +8183,10 @@
         <v>337</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>1008</v>
@@ -8098,7 +8200,7 @@
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>141</v>
@@ -8107,7 +8209,7 @@
         <v>142</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>541</v>
@@ -8122,10 +8224,10 @@
         <v>337</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1008</v>
@@ -8139,7 +8241,7 @@
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>143</v>
@@ -8148,7 +8250,7 @@
         <v>144</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>547</v>
@@ -8163,7 +8265,7 @@
         <v>348</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
@@ -8178,7 +8280,7 @@
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>145</v>
@@ -8187,7 +8289,7 @@
         <v>146</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>551</v>
@@ -8202,7 +8304,7 @@
         <v>348</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
@@ -8217,7 +8319,7 @@
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>147</v>
@@ -8226,7 +8328,7 @@
         <v>148</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>555</v>
@@ -8241,7 +8343,7 @@
         <v>348</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
@@ -8256,7 +8358,7 @@
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>149</v>
@@ -8265,7 +8367,7 @@
         <v>150</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>559</v>
@@ -8280,7 +8382,7 @@
         <v>348</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -8295,7 +8397,7 @@
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>151</v>
@@ -8304,7 +8406,7 @@
         <v>152</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>563</v>
@@ -8319,10 +8421,10 @@
         <v>337</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>1008</v>
@@ -8336,7 +8438,7 @@
     </row>
     <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>153</v>
@@ -8345,7 +8447,7 @@
         <v>154</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>568</v>
@@ -8360,10 +8462,10 @@
         <v>337</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>1008</v>
@@ -8377,7 +8479,7 @@
     </row>
     <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>155</v>
@@ -8386,7 +8488,7 @@
         <v>156</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>574</v>
@@ -8401,10 +8503,10 @@
         <v>337</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>1008</v>
@@ -8418,7 +8520,7 @@
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>159</v>
@@ -8427,7 +8529,7 @@
         <v>160</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>576</v>
@@ -8442,7 +8544,7 @@
         <v>348</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
@@ -8457,7 +8559,7 @@
     </row>
     <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>161</v>
@@ -8466,7 +8568,7 @@
         <v>162</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>580</v>
@@ -8481,10 +8583,10 @@
         <v>337</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>1008</v>
@@ -8498,7 +8600,7 @@
     </row>
     <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>163</v>
@@ -8507,7 +8609,7 @@
         <v>164</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>586</v>
@@ -8522,10 +8624,10 @@
         <v>337</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1008</v>
@@ -8539,7 +8641,7 @@
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>165</v>
@@ -8548,7 +8650,7 @@
         <v>166</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>592</v>
@@ -8563,10 +8665,10 @@
         <v>337</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>1008</v>
@@ -8580,7 +8682,7 @@
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>167</v>
@@ -8589,7 +8691,7 @@
         <v>168</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>598</v>
@@ -8604,7 +8706,7 @@
         <v>348</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
@@ -8619,7 +8721,7 @@
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>169</v>
@@ -8628,7 +8730,7 @@
         <v>170</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>602</v>
@@ -8643,7 +8745,7 @@
         <v>348</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -8658,7 +8760,7 @@
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>171</v>
@@ -8667,7 +8769,7 @@
         <v>172</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>606</v>
@@ -8682,7 +8784,7 @@
         <v>348</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -8697,7 +8799,7 @@
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>173</v>
@@ -8706,7 +8808,7 @@
         <v>174</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>610</v>
@@ -8721,7 +8823,7 @@
         <v>348</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -8736,7 +8838,7 @@
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>175</v>
@@ -8745,7 +8847,7 @@
         <v>176</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>614</v>
@@ -8760,7 +8862,7 @@
         <v>348</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -8775,7 +8877,7 @@
     </row>
     <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>177</v>
@@ -8784,7 +8886,7 @@
         <v>178</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>618</v>
@@ -8799,10 +8901,10 @@
         <v>337</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>1008</v>
@@ -8816,7 +8918,7 @@
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>179</v>
@@ -8825,7 +8927,7 @@
         <v>180</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>625</v>
@@ -8840,10 +8942,10 @@
         <v>337</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1008</v>
@@ -8857,7 +8959,7 @@
     </row>
     <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>181</v>
@@ -8866,7 +8968,7 @@
         <v>182</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>632</v>
@@ -8881,7 +8983,7 @@
         <v>348</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
@@ -8905,7 +9007,7 @@
         <v>184</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>636</v>
@@ -8920,10 +9022,10 @@
         <v>337</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>1008</v>
@@ -8946,7 +9048,7 @@
         <v>186</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>642</v>
@@ -8961,7 +9063,7 @@
         <v>348</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
@@ -8985,7 +9087,7 @@
         <v>188</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>646</v>
@@ -9000,7 +9102,7 @@
         <v>348</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
@@ -9024,7 +9126,7 @@
         <v>190</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>650</v>
@@ -9039,7 +9141,7 @@
         <v>348</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
@@ -9063,7 +9165,7 @@
         <v>192</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>654</v>
@@ -9078,7 +9180,7 @@
         <v>348</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
@@ -9093,7 +9195,7 @@
     </row>
     <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>193</v>
@@ -9102,7 +9204,7 @@
         <v>194</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>658</v>
@@ -9117,10 +9219,10 @@
         <v>337</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>1008</v>
@@ -9134,7 +9236,7 @@
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>195</v>
@@ -9143,7 +9245,7 @@
         <v>196</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>663</v>
@@ -9158,10 +9260,10 @@
         <v>337</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1008</v>
@@ -9175,7 +9277,7 @@
     </row>
     <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>197</v>
@@ -9184,7 +9286,7 @@
         <v>198</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>670</v>
@@ -9199,10 +9301,10 @@
         <v>337</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1008</v>
@@ -9216,7 +9318,7 @@
     </row>
     <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>199</v>
@@ -9225,7 +9327,7 @@
         <v>200</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>677</v>
@@ -9240,7 +9342,7 @@
         <v>348</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
@@ -9255,7 +9357,7 @@
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>201</v>
@@ -9264,7 +9366,7 @@
         <v>202</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>681</v>
@@ -9279,7 +9381,7 @@
         <v>348</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
@@ -9294,7 +9396,7 @@
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>203</v>
@@ -9303,7 +9405,7 @@
         <v>204</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>685</v>
@@ -9318,10 +9420,10 @@
         <v>337</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>1008</v>
@@ -9335,7 +9437,7 @@
     </row>
     <row r="71" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>205</v>
@@ -9344,7 +9446,7 @@
         <v>206</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>691</v>
@@ -9359,10 +9461,10 @@
         <v>337</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>1008</v>
@@ -9376,7 +9478,7 @@
     </row>
     <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>205</v>
@@ -9385,7 +9487,7 @@
         <v>206</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>698</v>
@@ -9400,10 +9502,10 @@
         <v>337</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1008</v>
@@ -9417,7 +9519,7 @@
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>207</v>
@@ -9426,7 +9528,7 @@
         <v>208</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>704</v>
@@ -9441,7 +9543,7 @@
         <v>348</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
@@ -9456,7 +9558,7 @@
     </row>
     <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>209</v>
@@ -9465,7 +9567,7 @@
         <v>210</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>708</v>
@@ -9480,10 +9582,10 @@
         <v>337</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>1008</v>
@@ -9497,7 +9599,7 @@
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>209</v>
@@ -9506,7 +9608,7 @@
         <v>210</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>715</v>
@@ -9521,10 +9623,10 @@
         <v>337</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>1008</v>
@@ -9538,7 +9640,7 @@
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>209</v>
@@ -9547,7 +9649,7 @@
         <v>210</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>721</v>
@@ -9562,10 +9664,10 @@
         <v>337</v>
       </c>
       <c r="I76" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="J76" s="2" t="s">
         <v>1351</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>1349</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>1008</v>
@@ -9579,7 +9681,7 @@
     </row>
     <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>211</v>
@@ -9588,7 +9690,7 @@
         <v>212</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>727</v>
@@ -9603,10 +9705,10 @@
         <v>337</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>1008</v>
@@ -9620,7 +9722,7 @@
     </row>
     <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>213</v>
@@ -9629,7 +9731,7 @@
         <v>214</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>734</v>
@@ -9644,7 +9746,7 @@
         <v>348</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
@@ -9659,7 +9761,7 @@
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>215</v>
@@ -9668,7 +9770,7 @@
         <v>216</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>738</v>
@@ -9683,7 +9785,7 @@
         <v>348</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -9707,7 +9809,7 @@
         <v>218</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>742</v>
@@ -9722,10 +9824,10 @@
         <v>337</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>1008</v>
@@ -9748,7 +9850,7 @@
         <v>220</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>748</v>
@@ -9763,10 +9865,10 @@
         <v>337</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1008</v>
@@ -9789,7 +9891,7 @@
         <v>222</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>754</v>
@@ -9804,10 +9906,10 @@
         <v>337</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>1008</v>
@@ -9830,7 +9932,7 @@
         <v>224</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>760</v>
@@ -9845,7 +9947,7 @@
         <v>348</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
@@ -9869,7 +9971,7 @@
         <v>226</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>764</v>
@@ -9884,7 +9986,7 @@
         <v>348</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -9908,7 +10010,7 @@
         <v>228</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>768</v>
@@ -9923,7 +10025,7 @@
         <v>348</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -9938,7 +10040,7 @@
     </row>
     <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>229</v>
@@ -9947,7 +10049,7 @@
         <v>230</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>772</v>
@@ -9962,10 +10064,10 @@
         <v>337</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>1008</v>
@@ -9979,7 +10081,7 @@
     </row>
     <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>231</v>
@@ -9988,7 +10090,7 @@
         <v>232</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>778</v>
@@ -10003,10 +10105,10 @@
         <v>337</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1008</v>
@@ -10020,7 +10122,7 @@
     </row>
     <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>233</v>
@@ -10029,7 +10131,7 @@
         <v>234</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>783</v>
@@ -10044,10 +10146,10 @@
         <v>337</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>1008</v>
@@ -10061,7 +10163,7 @@
     </row>
     <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>235</v>
@@ -10070,7 +10172,7 @@
         <v>236</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>789</v>
@@ -10085,10 +10187,10 @@
         <v>337</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>1008</v>
@@ -10102,7 +10204,7 @@
     </row>
     <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>237</v>
@@ -10111,7 +10213,7 @@
         <v>238</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>795</v>
@@ -10126,10 +10228,10 @@
         <v>337</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>1008</v>
@@ -10143,7 +10245,7 @@
     </row>
     <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>241</v>
@@ -10152,7 +10254,7 @@
         <v>242</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>797</v>
@@ -10167,7 +10269,7 @@
         <v>348</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
@@ -10182,7 +10284,7 @@
     </row>
     <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>243</v>
@@ -10191,7 +10293,7 @@
         <v>244</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>801</v>
@@ -10206,10 +10308,10 @@
         <v>337</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>1008</v>
@@ -10223,7 +10325,7 @@
     </row>
     <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>245</v>
@@ -10232,7 +10334,7 @@
         <v>246</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>803</v>
@@ -10247,7 +10349,7 @@
         <v>348</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
@@ -10262,7 +10364,7 @@
     </row>
     <row r="94" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>247</v>
@@ -10271,7 +10373,7 @@
         <v>248</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>807</v>
@@ -10286,10 +10388,10 @@
         <v>337</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>1008</v>
@@ -10303,7 +10405,7 @@
     </row>
     <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>249</v>
@@ -10312,7 +10414,7 @@
         <v>250</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>814</v>
@@ -10327,7 +10429,7 @@
         <v>348</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -10342,7 +10444,7 @@
     </row>
     <row r="96" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>251</v>
@@ -10351,7 +10453,7 @@
         <v>252</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>818</v>
@@ -10366,7 +10468,7 @@
         <v>348</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -10381,7 +10483,7 @@
     </row>
     <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>253</v>
@@ -10390,7 +10492,7 @@
         <v>254</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>822</v>
@@ -10405,7 +10507,7 @@
         <v>348</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -10420,7 +10522,7 @@
     </row>
     <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>255</v>
@@ -10429,7 +10531,7 @@
         <v>256</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>826</v>
@@ -10444,10 +10546,10 @@
         <v>337</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>1008</v>
@@ -10461,7 +10563,7 @@
     </row>
     <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>257</v>
@@ -10470,7 +10572,7 @@
         <v>258</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>832</v>
@@ -10485,7 +10587,7 @@
         <v>348</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -10500,7 +10602,7 @@
     </row>
     <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>259</v>
@@ -10509,7 +10611,7 @@
         <v>260</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>836</v>
@@ -10524,7 +10626,7 @@
         <v>348</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -10539,7 +10641,7 @@
     </row>
     <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>261</v>
@@ -10548,7 +10650,7 @@
         <v>262</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>840</v>
@@ -10563,7 +10665,7 @@
         <v>348</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -10578,7 +10680,7 @@
     </row>
     <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>263</v>
@@ -10587,7 +10689,7 @@
         <v>264</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>844</v>
@@ -10602,7 +10704,7 @@
         <v>348</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
@@ -10617,7 +10719,7 @@
     </row>
     <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>265</v>
@@ -10626,7 +10728,7 @@
         <v>266</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>848</v>
@@ -10641,7 +10743,7 @@
         <v>348</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -10656,7 +10758,7 @@
     </row>
     <row r="104" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>267</v>
@@ -10665,7 +10767,7 @@
         <v>268</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>852</v>
@@ -10680,10 +10782,10 @@
         <v>337</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>1008</v>
@@ -10697,7 +10799,7 @@
     </row>
     <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>269</v>
@@ -10706,7 +10808,7 @@
         <v>270</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>854</v>
@@ -10721,7 +10823,7 @@
         <v>348</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -10736,7 +10838,7 @@
     </row>
     <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>271</v>
@@ -10745,7 +10847,7 @@
         <v>272</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>858</v>
@@ -10760,10 +10862,10 @@
         <v>337</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1008</v>
@@ -10777,7 +10879,7 @@
     </row>
     <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>273</v>
@@ -10786,7 +10888,7 @@
         <v>274</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>864</v>
@@ -10801,7 +10903,7 @@
         <v>348</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2" t="s">
@@ -10816,7 +10918,7 @@
     </row>
     <row r="108" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>277</v>
@@ -10825,7 +10927,7 @@
         <v>278</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>868</v>
@@ -10840,7 +10942,7 @@
         <v>348</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="J108" s="2"/>
       <c r="K108" s="2" t="s">
@@ -10855,7 +10957,7 @@
     </row>
     <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>279</v>
@@ -10864,7 +10966,7 @@
         <v>280</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>872</v>
@@ -10879,7 +10981,7 @@
         <v>348</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
@@ -10894,7 +10996,7 @@
     </row>
     <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>281</v>
@@ -10903,7 +11005,7 @@
         <v>282</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>876</v>
@@ -10918,7 +11020,7 @@
         <v>348</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2" t="s">
@@ -10933,7 +11035,7 @@
     </row>
     <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>285</v>
@@ -10942,7 +11044,7 @@
         <v>286</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>880</v>
@@ -10957,7 +11059,7 @@
         <v>348</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="J111" s="2"/>
       <c r="K111" s="2" t="s">
@@ -10972,7 +11074,7 @@
     </row>
     <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>287</v>
@@ -10981,7 +11083,7 @@
         <v>288</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>884</v>
@@ -10996,7 +11098,7 @@
         <v>348</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2" t="s">
@@ -11011,7 +11113,7 @@
     </row>
     <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>289</v>
@@ -11020,7 +11122,7 @@
         <v>290</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>888</v>
@@ -11035,10 +11137,10 @@
         <v>337</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>1008</v>
@@ -11052,7 +11154,7 @@
     </row>
     <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>293</v>
@@ -11061,7 +11163,7 @@
         <v>294</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>893</v>
@@ -11076,7 +11178,7 @@
         <v>348</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
@@ -11091,7 +11193,7 @@
     </row>
     <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>295</v>
@@ -11100,7 +11202,7 @@
         <v>296</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>897</v>
@@ -11115,7 +11217,7 @@
         <v>348</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2" t="s">
@@ -11130,7 +11232,7 @@
     </row>
     <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>297</v>
@@ -11139,7 +11241,7 @@
         <v>298</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>901</v>
@@ -11154,7 +11256,7 @@
         <v>348</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
@@ -11169,7 +11271,7 @@
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>299</v>
@@ -11178,7 +11280,7 @@
         <v>300</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>905</v>
@@ -11193,10 +11295,10 @@
         <v>337</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1008</v>
@@ -11219,7 +11321,7 @@
         <v>302</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>911</v>
@@ -11234,10 +11336,10 @@
         <v>337</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>1008</v>
@@ -11260,7 +11362,7 @@
         <v>302</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>918</v>
@@ -11275,10 +11377,10 @@
         <v>337</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>1011</v>
@@ -11292,7 +11394,7 @@
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>303</v>
@@ -11301,7 +11403,7 @@
         <v>304</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>924</v>
@@ -11316,10 +11418,10 @@
         <v>337</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>1008</v>
@@ -11342,7 +11444,7 @@
         <v>306</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>930</v>
@@ -11357,10 +11459,10 @@
         <v>337</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>1008</v>
@@ -11383,7 +11485,7 @@
         <v>306</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>936</v>
@@ -11398,10 +11500,10 @@
         <v>337</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>1011</v>
@@ -11424,7 +11526,7 @@
         <v>306</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>940</v>
@@ -11439,10 +11541,10 @@
         <v>337</v>
       </c>
       <c r="I123" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="J123" s="2" t="s">
         <v>1461</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>1459</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>1008</v>
@@ -11465,7 +11567,7 @@
         <v>308</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>945</v>
@@ -11480,10 +11582,10 @@
         <v>337</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>1008</v>
@@ -11506,7 +11608,7 @@
         <v>308</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>952</v>
@@ -11521,10 +11623,10 @@
         <v>337</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1008</v>
@@ -11547,7 +11649,7 @@
         <v>308</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>958</v>
@@ -11562,10 +11664,10 @@
         <v>337</v>
       </c>
       <c r="I126" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="J126" s="2" t="s">
         <v>1466</v>
-      </c>
-      <c r="J126" s="2" t="s">
-        <v>1464</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1008</v>
@@ -11588,7 +11690,7 @@
         <v>308</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>963</v>
@@ -11603,10 +11705,10 @@
         <v>337</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>1008</v>
@@ -11629,7 +11731,7 @@
         <v>310</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>968</v>
@@ -11644,10 +11746,10 @@
         <v>337</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1008</v>
@@ -11670,7 +11772,7 @@
         <v>310</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>974</v>
@@ -11685,10 +11787,10 @@
         <v>337</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1008</v>
@@ -11711,7 +11813,7 @@
         <v>310</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>980</v>
@@ -11726,10 +11828,10 @@
         <v>337</v>
       </c>
       <c r="I130" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="J130" s="2" t="s">
         <v>1472</v>
-      </c>
-      <c r="J130" s="2" t="s">
-        <v>1470</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1008</v>
@@ -11752,7 +11854,7 @@
         <v>310</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>986</v>
@@ -11767,10 +11869,10 @@
         <v>337</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>1011</v>
@@ -11793,7 +11895,7 @@
         <v>312</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>992</v>
@@ -11808,10 +11910,10 @@
         <v>337</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1008</v>
@@ -11834,7 +11936,7 @@
         <v>312</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>998</v>
@@ -11849,10 +11951,10 @@
         <v>337</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1008</v>
@@ -11884,36 +11986,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
     </row>
   </sheetData>
@@ -11936,7 +12038,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>314</v>
@@ -11945,180 +12047,180 @@
         <v>1051</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
   </sheetData>
@@ -12141,186 +12243,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
     </row>
   </sheetData>
@@ -21201,7 +21303,7 @@
         <v>1008</v>
       </c>
       <c r="E8" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -21255,7 +21357,7 @@
         <v>1008</v>
       </c>
       <c r="E11" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -21273,7 +21375,7 @@
         <v>1008</v>
       </c>
       <c r="E12" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -21369,7 +21471,7 @@
         <v>1008</v>
       </c>
       <c r="E17" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -21387,7 +21489,7 @@
         <v>1008</v>
       </c>
       <c r="E18" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -21483,7 +21585,7 @@
         <v>1008</v>
       </c>
       <c r="E23" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -21501,7 +21603,7 @@
         <v>1008</v>
       </c>
       <c r="E24" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -21519,7 +21621,7 @@
         <v>1008</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -21537,7 +21639,7 @@
         <v>1008</v>
       </c>
       <c r="E26" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -21591,7 +21693,7 @@
         <v>1008</v>
       </c>
       <c r="E29" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -21609,7 +21711,7 @@
         <v>1008</v>
       </c>
       <c r="E30" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -21627,7 +21729,7 @@
         <v>1008</v>
       </c>
       <c r="E31" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -21741,7 +21843,7 @@
         <v>1008</v>
       </c>
       <c r="E37" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -21779,7 +21881,7 @@
         <v>1008</v>
       </c>
       <c r="E39" s="2">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -21797,7 +21899,7 @@
         <v>1008</v>
       </c>
       <c r="E40" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -21913,7 +22015,7 @@
         <v>1008</v>
       </c>
       <c r="E46" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -21931,7 +22033,7 @@
         <v>1008</v>
       </c>
       <c r="E47" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -21969,7 +22071,7 @@
         <v>1008</v>
       </c>
       <c r="E49" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -21987,7 +22089,7 @@
         <v>1008</v>
       </c>
       <c r="E50" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -22005,7 +22107,7 @@
         <v>1008</v>
       </c>
       <c r="E51" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -22123,7 +22225,7 @@
         <v>1008</v>
       </c>
       <c r="E57" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -22141,7 +22243,7 @@
         <v>1008</v>
       </c>
       <c r="E58" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -22179,7 +22281,7 @@
         <v>1008</v>
       </c>
       <c r="E60" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -22407,7 +22509,7 @@
         <v>1008</v>
       </c>
       <c r="E72" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -22463,7 +22565,7 @@
         <v>1008</v>
       </c>
       <c r="E75" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -22481,7 +22583,7 @@
         <v>1008</v>
       </c>
       <c r="E76" s="2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -22499,7 +22601,7 @@
         <v>1008</v>
       </c>
       <c r="E77" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -22557,7 +22659,7 @@
         <v>1008</v>
       </c>
       <c r="E80" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -22575,7 +22677,7 @@
         <v>1008</v>
       </c>
       <c r="E81" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -22593,7 +22695,7 @@
         <v>1008</v>
       </c>
       <c r="E82" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -22671,7 +22773,7 @@
         <v>1008</v>
       </c>
       <c r="E86" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -22689,7 +22791,7 @@
         <v>1008</v>
       </c>
       <c r="E87" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -22707,7 +22809,7 @@
         <v>1008</v>
       </c>
       <c r="E88" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -22725,7 +22827,7 @@
         <v>1008</v>
       </c>
       <c r="E89" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -22743,7 +22845,7 @@
         <v>1008</v>
       </c>
       <c r="E90" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -22781,7 +22883,7 @@
         <v>1008</v>
       </c>
       <c r="E92" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -22819,7 +22921,7 @@
         <v>1008</v>
       </c>
       <c r="E94" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -23015,7 +23117,7 @@
         <v>1008</v>
       </c>
       <c r="E104" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -23191,7 +23293,7 @@
         <v>1008</v>
       </c>
       <c r="E113" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -23287,7 +23389,7 @@
         <v>1008</v>
       </c>
       <c r="E118" s="2">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -23305,7 +23407,7 @@
         <v>1011</v>
       </c>
       <c r="E119" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -23323,7 +23425,7 @@
         <v>1008</v>
       </c>
       <c r="E120" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -23341,7 +23443,7 @@
         <v>1008</v>
       </c>
       <c r="E121" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -23377,7 +23479,7 @@
         <v>1008</v>
       </c>
       <c r="E123" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -23395,7 +23497,7 @@
         <v>1008</v>
       </c>
       <c r="E124" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -23413,7 +23515,7 @@
         <v>1008</v>
       </c>
       <c r="E125" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -23431,7 +23533,7 @@
         <v>1008</v>
       </c>
       <c r="E126" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -23485,7 +23587,7 @@
         <v>1008</v>
       </c>
       <c r="E129" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -23503,7 +23605,7 @@
         <v>1008</v>
       </c>
       <c r="E130" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -23521,7 +23623,7 @@
         <v>1011</v>
       </c>
       <c r="E131" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -23539,7 +23641,7 @@
         <v>1008</v>
       </c>
       <c r="E132" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F132" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/09-report/CYC-1-cycle-report.xlsx
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:25:46.538Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:28:28.630Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4543,7 +4543,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T20:25:47.603Z</t>
+    <t>2026-10-02T20:28:29.442Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -21185,7 +21185,7 @@
         <v>1008</v>
       </c>
       <c r="E2" s="2">
-        <v>506</v>
+        <v>548</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -21303,7 +21303,7 @@
         <v>1008</v>
       </c>
       <c r="E8" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -21321,7 +21321,7 @@
         <v>1008</v>
       </c>
       <c r="E9" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -21339,7 +21339,7 @@
         <v>1008</v>
       </c>
       <c r="E10" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -21357,7 +21357,7 @@
         <v>1008</v>
       </c>
       <c r="E11" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -21375,7 +21375,7 @@
         <v>1008</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -21393,7 +21393,7 @@
         <v>1008</v>
       </c>
       <c r="E13" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -21471,7 +21471,7 @@
         <v>1008</v>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -21489,7 +21489,7 @@
         <v>1008</v>
       </c>
       <c r="E18" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -21547,7 +21547,7 @@
         <v>1008</v>
       </c>
       <c r="E21" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -21603,7 +21603,7 @@
         <v>1008</v>
       </c>
       <c r="E24" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -21621,7 +21621,7 @@
         <v>1008</v>
       </c>
       <c r="E25" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -21657,7 +21657,7 @@
         <v>1008</v>
       </c>
       <c r="E27" s="2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -21675,7 +21675,7 @@
         <v>1008</v>
       </c>
       <c r="E28" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -21693,7 +21693,7 @@
         <v>1008</v>
       </c>
       <c r="E29" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -21711,7 +21711,7 @@
         <v>1008</v>
       </c>
       <c r="E30" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -21729,7 +21729,7 @@
         <v>1008</v>
       </c>
       <c r="E31" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -21767,7 +21767,7 @@
         <v>1008</v>
       </c>
       <c r="E33" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -21881,7 +21881,7 @@
         <v>1008</v>
       </c>
       <c r="E39" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -21899,7 +21899,7 @@
         <v>1008</v>
       </c>
       <c r="E40" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -21997,7 +21997,7 @@
         <v>1008</v>
       </c>
       <c r="E45" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -22015,7 +22015,7 @@
         <v>1008</v>
       </c>
       <c r="E46" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -22033,7 +22033,7 @@
         <v>1008</v>
       </c>
       <c r="E47" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -22071,7 +22071,7 @@
         <v>1008</v>
       </c>
       <c r="E49" s="2">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -22089,7 +22089,7 @@
         <v>1008</v>
       </c>
       <c r="E50" s="2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -22107,7 +22107,7 @@
         <v>1008</v>
       </c>
       <c r="E51" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -22225,7 +22225,7 @@
         <v>1008</v>
       </c>
       <c r="E57" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -22243,7 +22243,7 @@
         <v>1008</v>
       </c>
       <c r="E58" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -22281,7 +22281,7 @@
         <v>1008</v>
       </c>
       <c r="E60" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -22397,7 +22397,7 @@
         <v>1008</v>
       </c>
       <c r="E66" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -22415,7 +22415,7 @@
         <v>1008</v>
       </c>
       <c r="E67" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -22473,7 +22473,7 @@
         <v>1008</v>
       </c>
       <c r="E70" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -22491,7 +22491,7 @@
         <v>1008</v>
       </c>
       <c r="E71" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -22509,7 +22509,7 @@
         <v>1008</v>
       </c>
       <c r="E72" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -22547,7 +22547,7 @@
         <v>1008</v>
       </c>
       <c r="E74" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -22565,7 +22565,7 @@
         <v>1008</v>
       </c>
       <c r="E75" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -22583,7 +22583,7 @@
         <v>1008</v>
       </c>
       <c r="E76" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -22601,7 +22601,7 @@
         <v>1008</v>
       </c>
       <c r="E77" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -22659,7 +22659,7 @@
         <v>1008</v>
       </c>
       <c r="E80" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -22677,7 +22677,7 @@
         <v>1008</v>
       </c>
       <c r="E81" s="2">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -22695,7 +22695,7 @@
         <v>1008</v>
       </c>
       <c r="E82" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -22773,7 +22773,7 @@
         <v>1008</v>
       </c>
       <c r="E86" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -22809,7 +22809,7 @@
         <v>1008</v>
       </c>
       <c r="E88" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -22827,7 +22827,7 @@
         <v>1008</v>
       </c>
       <c r="E89" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -22845,7 +22845,7 @@
         <v>1008</v>
       </c>
       <c r="E90" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -22883,7 +22883,7 @@
         <v>1008</v>
       </c>
       <c r="E92" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -22921,7 +22921,7 @@
         <v>1008</v>
       </c>
       <c r="E94" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -23293,7 +23293,7 @@
         <v>1008</v>
       </c>
       <c r="E113" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -23371,7 +23371,7 @@
         <v>1008</v>
       </c>
       <c r="E117" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -23389,7 +23389,7 @@
         <v>1008</v>
       </c>
       <c r="E118" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -23407,7 +23407,7 @@
         <v>1011</v>
       </c>
       <c r="E119" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -23425,7 +23425,7 @@
         <v>1008</v>
       </c>
       <c r="E120" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -23461,7 +23461,7 @@
         <v>1011</v>
       </c>
       <c r="E122" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -23479,7 +23479,7 @@
         <v>1008</v>
       </c>
       <c r="E123" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -23497,7 +23497,7 @@
         <v>1008</v>
       </c>
       <c r="E124" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -23515,7 +23515,7 @@
         <v>1008</v>
       </c>
       <c r="E125" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -23533,7 +23533,7 @@
         <v>1008</v>
       </c>
       <c r="E126" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -23551,7 +23551,7 @@
         <v>1008</v>
       </c>
       <c r="E127" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -23569,7 +23569,7 @@
         <v>1008</v>
       </c>
       <c r="E128" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -23587,7 +23587,7 @@
         <v>1008</v>
       </c>
       <c r="E129" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -23623,7 +23623,7 @@
         <v>1011</v>
       </c>
       <c r="E131" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -23659,7 +23659,7 @@
         <v>1008</v>
       </c>
       <c r="E133" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F133" s="2"/>
     </row>
